--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_27aug26_Thurs.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_27aug26_Thurs.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AVITA\projects\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C307B9D-C307-4DAA-A3B1-2F3931554ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10296"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sheet1 (2)'!$A$1:$O$271</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$L$20</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -726,7 +727,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -862,7 +863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1029,34 +1030,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="15" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -1066,26 +1039,11 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1388,28 +1346,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:O270"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="12"/>
-    <col min="4" max="5" width="8.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="12"/>
-    <col min="10" max="10" width="10.5546875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" style="12"/>
+    <col min="4" max="5" width="8.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="12"/>
+    <col min="10" max="10" width="10.54296875" style="20" customWidth="1"/>
     <col min="11" max="11" width="19" style="20" customWidth="1"/>
-    <col min="12" max="13" width="8.88671875" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="12"/>
-    <col min="15" max="15" width="8.77734375" style="20"/>
-    <col min="16" max="16384" width="8.77734375" style="12"/>
+    <col min="12" max="13" width="8.90625" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.81640625" style="12"/>
+    <col min="15" max="15" width="8.81640625" style="20"/>
+    <col min="16" max="16384" width="8.81640625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1450,7 +1408,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46261.375810185185</v>
       </c>
@@ -1492,12 +1450,12 @@
         <v>250</v>
       </c>
       <c r="N2" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B2, $C$2:$C$895, C2, $D$2:$D$895, D2, $E$2:$E$895, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$895, B2, $C$2:$C$895, C2, $D$2:$D$895, D2, $E$2:$E$895, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>46260.375</v>
       </c>
@@ -1539,12 +1497,12 @@
         <v>10780</v>
       </c>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B3, $C$2:$C$895, C3, $D$2:$D$895, D3, $E$2:$E$895, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="20"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -1577,12 +1535,12 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B4, $C$2:$C$895, C4, $D$2:$D$895, D4, $E$2:$E$895, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>46261.450868055559</v>
       </c>
@@ -1624,12 +1582,12 @@
         <v>300</v>
       </c>
       <c r="N5" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B5, $C$2:$C$895, C5, $D$2:$D$895, D5, $E$2:$E$895, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="20"/>
     </row>
-    <row r="6" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -1664,12 +1622,12 @@
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B6, $C$2:$C$895, C6, $D$2:$D$895, D6, $E$2:$E$895, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>46252.6875</v>
       </c>
@@ -1704,12 +1662,12 @@
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B7, $C$2:$C$895, C7, $D$2:$D$895, D7, $E$2:$E$895, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="19"/>
     </row>
-    <row r="8" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -1744,12 +1702,12 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B8, $C$2:$C$895, C8, $D$2:$D$895, D8, $E$2:$E$895, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="19"/>
     </row>
-    <row r="9" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="3">
         <v>46258.613194444442</v>
       </c>
@@ -1791,12 +1749,12 @@
         <v>300</v>
       </c>
       <c r="N9" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B9, $C$2:$C$895, C9, $D$2:$D$895, D9, $E$2:$E$895, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="20"/>
     </row>
-    <row r="10" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>46261.461388888885</v>
       </c>
@@ -1838,12 +1796,12 @@
         <v>675</v>
       </c>
       <c r="N10" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B10, $C$2:$C$895, C10, $D$2:$D$895, D10, $E$2:$E$895, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="20"/>
     </row>
-    <row r="11" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>150</v>
       </c>
@@ -1880,12 +1838,12 @@
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B11, $C$2:$C$895, C11, $D$2:$D$895, D11, $E$2:$E$895, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="19"/>
     </row>
-    <row r="12" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1918,12 +1876,12 @@
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B12, $C$2:$C$895, C12, $D$2:$D$895, D12, $E$2:$E$895, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1958,12 +1916,12 @@
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B13, $C$2:$C$895, C13, $D$2:$D$895, D13, $E$2:$E$895, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="19"/>
     </row>
-    <row r="14" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>46260.375</v>
       </c>
@@ -2005,12 +1963,12 @@
         <v>5798</v>
       </c>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B14, $C$2:$C$895, C14, $D$2:$D$895, D14, $E$2:$E$895, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="20"/>
     </row>
-    <row r="15" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>46260.375</v>
       </c>
@@ -2052,12 +2010,12 @@
         <v>460</v>
       </c>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B15, $C$2:$C$895, C15, $D$2:$D$895, D15, $E$2:$E$895, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O15" s="20"/>
     </row>
-    <row r="16" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>46260.375</v>
       </c>
@@ -2099,12 +2057,12 @@
         <v>340</v>
       </c>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B16, $C$2:$C$895, C16, $D$2:$D$895, D16, $E$2:$E$895, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O16" s="20"/>
     </row>
-    <row r="17" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -2139,12 +2097,12 @@
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B17, $C$2:$C$895, C17, $D$2:$D$895, D17, $E$2:$E$895, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="19"/>
     </row>
-    <row r="18" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -2181,12 +2139,12 @@
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B18, $C$2:$C$895, C18, $D$2:$D$895, D18, $E$2:$E$895, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="19"/>
     </row>
-    <row r="19" spans="1:15" s="57" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" s="57" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="22">
         <v>46255</v>
       </c>
@@ -2228,12 +2186,12 @@
         <v>300</v>
       </c>
       <c r="N19" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B19, $C$2:$C$895, C19, $D$2:$D$895, D19, $E$2:$E$895, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="20"/>
     </row>
-    <row r="20" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>46254.375</v>
       </c>
@@ -2270,12 +2228,12 @@
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B20, $C$2:$C$895, C20, $D$2:$D$895, D20, $E$2:$E$895, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="19"/>
     </row>
-    <row r="21" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>46252.6875</v>
       </c>
@@ -2308,12 +2266,12 @@
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B21, $C$2:$C$895, C21, $D$2:$D$895, D21, $E$2:$E$895, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="19"/>
     </row>
-    <row r="22" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -2355,12 +2313,12 @@
         <v>750</v>
       </c>
       <c r="N22" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B22, $C$2:$C$895, C22, $D$2:$D$895, D22, $E$2:$E$895, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="20"/>
     </row>
-    <row r="23" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
@@ -2395,12 +2353,12 @@
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B23, $C$2:$C$895, C23, $D$2:$D$895, D23, $E$2:$E$895, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="19"/>
     </row>
-    <row r="24" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
@@ -2435,12 +2393,12 @@
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B24, $C$2:$C$895, C24, $D$2:$D$895, D24, $E$2:$E$895, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="19"/>
     </row>
-    <row r="25" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -2475,12 +2433,12 @@
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B25, $C$2:$C$895, C25, $D$2:$D$895, D25, $E$2:$E$895, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="19"/>
     </row>
-    <row r="26" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>46252.6875</v>
       </c>
@@ -2515,12 +2473,12 @@
       <c r="L26" s="19"/>
       <c r="M26" s="19"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B26, $C$2:$C$895, C26, $D$2:$D$895, D26, $E$2:$E$895, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="19"/>
     </row>
-    <row r="27" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>62</v>
       </c>
@@ -2553,12 +2511,12 @@
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B27, $C$2:$C$895, C27, $D$2:$D$895, D27, $E$2:$E$895, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="19"/>
     </row>
-    <row r="28" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="3">
         <v>46258.459722222222</v>
       </c>
@@ -2600,12 +2558,12 @@
         <v>295</v>
       </c>
       <c r="N28" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B28, $C$2:$C$895, C28, $D$2:$D$895, D28, $E$2:$E$895, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="20"/>
     </row>
-    <row r="29" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <v>46252.6875</v>
       </c>
@@ -2638,12 +2596,12 @@
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B29, $C$2:$C$895, C29, $D$2:$D$895, D29, $E$2:$E$895, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="19"/>
     </row>
-    <row r="30" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>46261.375555555554</v>
       </c>
@@ -2685,12 +2643,12 @@
         <v>300</v>
       </c>
       <c r="N30" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B30, $C$2:$C$895, C30, $D$2:$D$895, D30, $E$2:$E$895, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="20"/>
     </row>
-    <row r="31" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2725,12 +2683,12 @@
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B31, $C$2:$C$895, C31, $D$2:$D$895, D31, $E$2:$E$895, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="19"/>
     </row>
-    <row r="32" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -2763,12 +2721,12 @@
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B32, $C$2:$C$895, C32, $D$2:$D$895, D32, $E$2:$E$895, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="19"/>
     </row>
-    <row r="33" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
         <v>46261.375567129631</v>
       </c>
@@ -2796,26 +2754,26 @@
       <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J33" s="72" t="s">
+      <c r="J33" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="K33" s="60" t="s">
+      <c r="K33" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="L33" s="60">
+      <c r="L33" s="20">
         <v>8760</v>
       </c>
-      <c r="M33" s="60">
+      <c r="M33" s="20">
         <f>ABS((D33*E33)-L33)</f>
         <v>320</v>
       </c>
-      <c r="N33" s="59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B33, $C$2:$C$895, C33, $D$2:$D$895, D33, $E$2:$E$895, E33) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O33" s="60"/>
-    </row>
-    <row r="34" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="N33" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+      <c r="O33" s="20"/>
+    </row>
+    <row r="34" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <v>46253.375</v>
       </c>
@@ -2850,12 +2808,12 @@
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B34, $C$2:$C$895, C34, $D$2:$D$895, D34, $E$2:$E$895, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="19"/>
     </row>
-    <row r="35" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
@@ -2888,12 +2846,12 @@
       <c r="L35" s="19"/>
       <c r="M35" s="19"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B35, $C$2:$C$895, C35, $D$2:$D$895, D35, $E$2:$E$895, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="19"/>
     </row>
-    <row r="36" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <v>46252.6875</v>
       </c>
@@ -2926,12 +2884,12 @@
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B36, $C$2:$C$895, C36, $D$2:$D$895, D36, $E$2:$E$895, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="19"/>
     </row>
-    <row r="37" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="3">
         <v>46261.375555555554</v>
       </c>
@@ -2973,12 +2931,12 @@
         <v>700</v>
       </c>
       <c r="N37" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B37, $C$2:$C$895, C37, $D$2:$D$895, D37, $E$2:$E$895, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="20"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -3013,12 +2971,12 @@
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B38, $C$2:$C$895, C38, $D$2:$D$895, D38, $E$2:$E$895, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="19"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <v>46260.375</v>
       </c>
@@ -3060,12 +3018,12 @@
         <v>5888</v>
       </c>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B39, $C$2:$C$895, C39, $D$2:$D$895, D39, $E$2:$E$895, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="20"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="6" t="s">
         <v>62</v>
       </c>
@@ -3098,12 +3056,12 @@
       <c r="L40" s="19"/>
       <c r="M40" s="19"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B40, $C$2:$C$895, C40, $D$2:$D$895, D40, $E$2:$E$895, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="19"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
@@ -3136,12 +3094,12 @@
       <c r="L41" s="19"/>
       <c r="M41" s="19"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B41, $C$2:$C$895, C41, $D$2:$D$895, D41, $E$2:$E$895, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41" s="19"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="6" t="s">
         <v>62</v>
       </c>
@@ -3174,12 +3132,12 @@
       <c r="L42" s="19"/>
       <c r="M42" s="19"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B42, $C$2:$C$895, C42, $D$2:$D$895, D42, $E$2:$E$895, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42" s="19"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="3">
         <v>46260.375</v>
       </c>
@@ -3221,12 +3179,12 @@
         <v>680</v>
       </c>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B43, $C$2:$C$895, C43, $D$2:$D$895, D43, $E$2:$E$895, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="20"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -3268,12 +3226,12 @@
         <v>300</v>
       </c>
       <c r="N44" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B44, $C$2:$C$895, C44, $D$2:$D$895, D44, $E$2:$E$895, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="20"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="6" t="s">
         <v>62</v>
       </c>
@@ -3306,12 +3264,12 @@
       <c r="L45" s="19"/>
       <c r="M45" s="19"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B45, $C$2:$C$895, C45, $D$2:$D$895, D45, $E$2:$E$895, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="19"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -3348,12 +3306,12 @@
       <c r="L46" s="19"/>
       <c r="M46" s="19"/>
       <c r="N46" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B46, $C$2:$C$895, C46, $D$2:$D$895, D46, $E$2:$E$895, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="19"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3388,12 +3346,12 @@
       <c r="L47" s="19"/>
       <c r="M47" s="19"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B47, $C$2:$C$895, C47, $D$2:$D$895, D47, $E$2:$E$895, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47" s="19"/>
     </row>
-    <row r="48" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="6" t="s">
         <v>62</v>
       </c>
@@ -3426,12 +3384,12 @@
       <c r="L48" s="19"/>
       <c r="M48" s="19"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B48, $C$2:$C$895, C48, $D$2:$D$895, D48, $E$2:$E$895, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="19"/>
     </row>
-    <row r="49" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <v>46252.6875</v>
       </c>
@@ -3466,12 +3424,12 @@
       <c r="L49" s="19"/>
       <c r="M49" s="19"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B49, $C$2:$C$895, C49, $D$2:$D$895, D49, $E$2:$E$895, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="19"/>
     </row>
-    <row r="50" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -3506,25 +3464,25 @@
       <c r="L50" s="19"/>
       <c r="M50" s="19"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B50, $C$2:$C$895, C50, $D$2:$D$895, D50, $E$2:$E$895, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="19"/>
     </row>
-    <row r="51" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="68">
+    <row r="51" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="58">
         <v>46255</v>
       </c>
-      <c r="B51" s="69" t="s">
+      <c r="B51" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="70">
+      <c r="C51" s="59" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="60">
         <v>1</v>
       </c>
-      <c r="E51" s="70">
+      <c r="E51" s="60">
         <v>19652</v>
       </c>
       <c r="F51" s="4">
@@ -3553,12 +3511,12 @@
         <v>340</v>
       </c>
       <c r="N51" s="56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B51, $C$2:$C$895, C51, $D$2:$D$895, D51, $E$2:$E$895, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="55"/>
     </row>
-    <row r="52" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="6" t="s">
         <v>62</v>
       </c>
@@ -3591,12 +3549,12 @@
       <c r="L52" s="19"/>
       <c r="M52" s="19"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B52, $C$2:$C$895, C52, $D$2:$D$895, D52, $E$2:$E$895, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="19"/>
     </row>
-    <row r="53" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3631,12 +3589,12 @@
       <c r="L53" s="19"/>
       <c r="M53" s="19"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B53, $C$2:$C$895, C53, $D$2:$D$895, D53, $E$2:$E$895, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53" s="19"/>
     </row>
-    <row r="54" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
@@ -3669,12 +3627,12 @@
       <c r="L54" s="19"/>
       <c r="M54" s="19"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B54, $C$2:$C$895, C54, $D$2:$D$895, D54, $E$2:$E$895, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="19"/>
     </row>
-    <row r="55" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -3709,12 +3667,12 @@
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B55, $C$2:$C$895, C55, $D$2:$D$895, D55, $E$2:$E$895, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="19"/>
     </row>
-    <row r="56" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
         <v>46260.375</v>
       </c>
@@ -3756,12 +3714,12 @@
         <v>300</v>
       </c>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B56, $C$2:$C$895, C56, $D$2:$D$895, D56, $E$2:$E$895, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="20"/>
     </row>
-    <row r="57" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3796,12 +3754,12 @@
       <c r="L57" s="19"/>
       <c r="M57" s="19"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B57, $C$2:$C$895, C57, $D$2:$D$895, D57, $E$2:$E$895, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57" s="19"/>
     </row>
-    <row r="58" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="6" t="s">
         <v>62</v>
       </c>
@@ -3834,12 +3792,12 @@
       <c r="L58" s="19"/>
       <c r="M58" s="19"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B58, $C$2:$C$895, C58, $D$2:$D$895, D58, $E$2:$E$895, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58" s="19"/>
     </row>
-    <row r="59" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="3">
         <v>46261.375555555554</v>
       </c>
@@ -3881,12 +3839,12 @@
         <v>300</v>
       </c>
       <c r="N59" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B59, $C$2:$C$895, C59, $D$2:$D$895, D59, $E$2:$E$895, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="20"/>
     </row>
-    <row r="60" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3921,12 +3879,12 @@
       <c r="L60" s="19"/>
       <c r="M60" s="19"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B60, $C$2:$C$895, C60, $D$2:$D$895, D60, $E$2:$E$895, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="19"/>
     </row>
-    <row r="61" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
@@ -3959,12 +3917,12 @@
       <c r="L61" s="19"/>
       <c r="M61" s="19"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B61, $C$2:$C$895, C61, $D$2:$D$895, D61, $E$2:$E$895, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="19"/>
     </row>
-    <row r="62" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
@@ -3997,12 +3955,12 @@
       <c r="L62" s="19"/>
       <c r="M62" s="19"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B62, $C$2:$C$895, C62, $D$2:$D$895, D62, $E$2:$E$895, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="19"/>
     </row>
-    <row r="63" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
         <v>46252.6875</v>
       </c>
@@ -4035,12 +3993,12 @@
       <c r="L63" s="19"/>
       <c r="M63" s="19"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B63, $C$2:$C$895, C63, $D$2:$D$895, D63, $E$2:$E$895, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="19"/>
     </row>
-    <row r="64" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4075,12 +4033,12 @@
       <c r="L64" s="19"/>
       <c r="M64" s="19"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B64, $C$2:$C$895, C64, $D$2:$D$895, D64, $E$2:$E$895, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="19"/>
     </row>
-    <row r="65" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="6" t="s">
         <v>62</v>
       </c>
@@ -4113,12 +4071,12 @@
       <c r="L65" s="19"/>
       <c r="M65" s="19"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B65, $C$2:$C$895, C65, $D$2:$D$895, D65, $E$2:$E$895, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="19"/>
     </row>
-    <row r="66" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6" t="s">
         <v>62</v>
       </c>
@@ -4151,12 +4109,12 @@
       <c r="L66" s="19"/>
       <c r="M66" s="19"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B66, $C$2:$C$895, C66, $D$2:$D$895, D66, $E$2:$E$895, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$895, B66, $C$2:$C$895, C66, $D$2:$D$895, D66, $E$2:$E$895, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66" s="19"/>
     </row>
-    <row r="67" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="6" t="s">
         <v>62</v>
       </c>
@@ -4189,12 +4147,12 @@
       <c r="L67" s="19"/>
       <c r="M67" s="19"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B67, $C$2:$C$895, C67, $D$2:$D$895, D67, $E$2:$E$895, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="19"/>
     </row>
-    <row r="68" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -4229,12 +4187,12 @@
       <c r="L68" s="19"/>
       <c r="M68" s="19"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B68, $C$2:$C$895, C68, $D$2:$D$895, D68, $E$2:$E$895, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="19"/>
     </row>
-    <row r="69" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
@@ -4267,12 +4225,12 @@
       <c r="L69" s="19"/>
       <c r="M69" s="19"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B69, $C$2:$C$895, C69, $D$2:$D$895, D69, $E$2:$E$895, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="19"/>
     </row>
-    <row r="70" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="6" t="s">
         <v>62</v>
       </c>
@@ -4300,17 +4258,17 @@
       <c r="I70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J70" s="66"/>
-      <c r="K70" s="67"/>
-      <c r="L70" s="67"/>
-      <c r="M70" s="67"/>
-      <c r="N70" s="58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B70, $C$2:$C$895, C70, $D$2:$D$895, D70, $E$2:$E$895, E70) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O70" s="67"/>
-    </row>
-    <row r="71" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J70" s="25"/>
+      <c r="K70" s="19"/>
+      <c r="L70" s="19"/>
+      <c r="M70" s="19"/>
+      <c r="N70" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+      <c r="O70" s="19"/>
+    </row>
+    <row r="71" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="6" t="s">
         <v>62</v>
       </c>
@@ -4343,12 +4301,12 @@
       <c r="L71" s="19"/>
       <c r="M71" s="19"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B71, $C$2:$C$895, C71, $D$2:$D$895, D71, $E$2:$E$895, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="19"/>
     </row>
-    <row r="72" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="3">
         <v>46252.6875</v>
       </c>
@@ -4383,12 +4341,12 @@
       <c r="L72" s="19"/>
       <c r="M72" s="19"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B72, $C$2:$C$895, C72, $D$2:$D$895, D72, $E$2:$E$895, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72" s="19"/>
     </row>
-    <row r="73" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="6" t="s">
         <v>62</v>
       </c>
@@ -4421,12 +4379,12 @@
       <c r="L73" s="19"/>
       <c r="M73" s="19"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B73, $C$2:$C$895, C73, $D$2:$D$895, D73, $E$2:$E$895, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="19"/>
     </row>
-    <row r="74" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -4468,12 +4426,12 @@
         <v>580</v>
       </c>
       <c r="N74" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B74, $C$2:$C$895, C74, $D$2:$D$895, D74, $E$2:$E$895, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="20"/>
     </row>
-    <row r="75" spans="1:15" s="58" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="6" t="s">
         <v>62</v>
       </c>
@@ -4506,12 +4464,12 @@
       <c r="L75" s="19"/>
       <c r="M75" s="19"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B75, $C$2:$C$895, C75, $D$2:$D$895, D75, $E$2:$E$895, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="19"/>
     </row>
-    <row r="76" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="6" t="s">
         <v>62</v>
       </c>
@@ -4544,12 +4502,12 @@
       <c r="L76" s="19"/>
       <c r="M76" s="19"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B76, $C$2:$C$895, C76, $D$2:$D$895, D76, $E$2:$E$895, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="19"/>
     </row>
-    <row r="77" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4582,12 +4540,12 @@
       <c r="L77" s="19"/>
       <c r="M77" s="19"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B77, $C$2:$C$895, C77, $D$2:$D$895, D77, $E$2:$E$895, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="19"/>
     </row>
-    <row r="78" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
         <v>46261.375509259262</v>
       </c>
@@ -4629,12 +4587,12 @@
         <v>300</v>
       </c>
       <c r="N78" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B78, $C$2:$C$895, C78, $D$2:$D$895, D78, $E$2:$E$895, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="20"/>
     </row>
-    <row r="79" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="6" t="s">
         <v>62</v>
       </c>
@@ -4667,12 +4625,12 @@
       <c r="L79" s="19"/>
       <c r="M79" s="19"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B79, $C$2:$C$895, C79, $D$2:$D$895, D79, $E$2:$E$895, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="19"/>
     </row>
-    <row r="80" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
@@ -4705,12 +4663,12 @@
       <c r="L80" s="19"/>
       <c r="M80" s="19"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B80, $C$2:$C$895, C80, $D$2:$D$895, D80, $E$2:$E$895, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="19"/>
     </row>
-    <row r="81" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="6" t="s">
         <v>62</v>
       </c>
@@ -4743,12 +4701,12 @@
       <c r="L81" s="19"/>
       <c r="M81" s="19"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B81, $C$2:$C$895, C81, $D$2:$D$895, D81, $E$2:$E$895, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="19"/>
     </row>
-    <row r="82" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="6" t="s">
         <v>62</v>
       </c>
@@ -4781,12 +4739,12 @@
       <c r="L82" s="19"/>
       <c r="M82" s="19"/>
       <c r="N82" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B82, $C$2:$C$895, C82, $D$2:$D$895, D82, $E$2:$E$895, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82" s="19"/>
     </row>
-    <row r="83" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -4819,12 +4777,12 @@
       <c r="L83" s="19"/>
       <c r="M83" s="19"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B83, $C$2:$C$895, C83, $D$2:$D$895, D83, $E$2:$E$895, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83" s="19"/>
     </row>
-    <row r="84" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="3">
         <v>46252.6875</v>
       </c>
@@ -4859,12 +4817,12 @@
       <c r="L84" s="19"/>
       <c r="M84" s="19"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B84, $C$2:$C$895, C84, $D$2:$D$895, D84, $E$2:$E$895, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="19"/>
     </row>
-    <row r="85" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="6" t="s">
         <v>62</v>
       </c>
@@ -4897,12 +4855,12 @@
       <c r="L85" s="19"/>
       <c r="M85" s="19"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B85, $C$2:$C$895, C85, $D$2:$D$895, D85, $E$2:$E$895, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="19"/>
     </row>
-    <row r="86" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4935,12 +4893,12 @@
       <c r="L86" s="19"/>
       <c r="M86" s="19"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B86, $C$2:$C$895, C86, $D$2:$D$895, D86, $E$2:$E$895, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="19"/>
     </row>
-    <row r="87" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
@@ -4973,12 +4931,12 @@
       <c r="L87" s="19"/>
       <c r="M87" s="19"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B87, $C$2:$C$895, C87, $D$2:$D$895, D87, $E$2:$E$895, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="19"/>
     </row>
-    <row r="88" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
@@ -5011,12 +4969,12 @@
       <c r="L88" s="19"/>
       <c r="M88" s="19"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B88, $C$2:$C$895, C88, $D$2:$D$895, D88, $E$2:$E$895, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="19"/>
     </row>
-    <row r="89" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="6" t="s">
         <v>62</v>
       </c>
@@ -5049,12 +5007,12 @@
       <c r="L89" s="19"/>
       <c r="M89" s="19"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B89, $C$2:$C$895, C89, $D$2:$D$895, D89, $E$2:$E$895, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89" s="19"/>
     </row>
-    <row r="90" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="6" t="s">
         <v>62</v>
       </c>
@@ -5087,12 +5045,12 @@
       <c r="L90" s="19"/>
       <c r="M90" s="19"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B90, $C$2:$C$895, C90, $D$2:$D$895, D90, $E$2:$E$895, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="19"/>
     </row>
-    <row r="91" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="3">
         <v>46252.6875</v>
       </c>
@@ -5127,12 +5085,12 @@
       <c r="L91" s="19"/>
       <c r="M91" s="19"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B91, $C$2:$C$895, C91, $D$2:$D$895, D91, $E$2:$E$895, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="19"/>
     </row>
-    <row r="92" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="6" t="s">
         <v>62</v>
       </c>
@@ -5165,12 +5123,12 @@
       <c r="L92" s="19"/>
       <c r="M92" s="19"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B92, $C$2:$C$895, C92, $D$2:$D$895, D92, $E$2:$E$895, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="19"/>
     </row>
-    <row r="93" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="6" t="s">
         <v>62</v>
       </c>
@@ -5203,12 +5161,12 @@
       <c r="L93" s="19"/>
       <c r="M93" s="19"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B93, $C$2:$C$895, C93, $D$2:$D$895, D93, $E$2:$E$895, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="19"/>
     </row>
-    <row r="94" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="6" t="s">
         <v>62</v>
       </c>
@@ -5241,12 +5199,12 @@
       <c r="L94" s="19"/>
       <c r="M94" s="19"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B94, $C$2:$C$895, C94, $D$2:$D$895, D94, $E$2:$E$895, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="19"/>
     </row>
-    <row r="95" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="6" t="s">
         <v>62</v>
       </c>
@@ -5279,12 +5237,12 @@
       <c r="L95" s="19"/>
       <c r="M95" s="19"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B95, $C$2:$C$895, C95, $D$2:$D$895, D95, $E$2:$E$895, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="19"/>
     </row>
-    <row r="96" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="22">
         <v>46255</v>
       </c>
@@ -5326,12 +5284,12 @@
         <v>300</v>
       </c>
       <c r="N96" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B96, $C$2:$C$895, C96, $D$2:$D$895, D96, $E$2:$E$895, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="20"/>
     </row>
-    <row r="97" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="6" t="s">
         <v>62</v>
       </c>
@@ -5364,12 +5322,12 @@
       <c r="L97" s="19"/>
       <c r="M97" s="19"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B97, $C$2:$C$895, C97, $D$2:$D$895, D97, $E$2:$E$895, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="19"/>
     </row>
-    <row r="98" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="6" t="s">
         <v>62</v>
       </c>
@@ -5402,12 +5360,12 @@
       <c r="L98" s="19"/>
       <c r="M98" s="19"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B98, $C$2:$C$895, C98, $D$2:$D$895, D98, $E$2:$E$895, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="19"/>
     </row>
-    <row r="99" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46253.416666666664</v>
       </c>
@@ -5442,12 +5400,12 @@
       <c r="L99" s="19"/>
       <c r="M99" s="19"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B99, $C$2:$C$895, C99, $D$2:$D$895, D99, $E$2:$E$895, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="19"/>
     </row>
-    <row r="100" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46252.6875</v>
       </c>
@@ -5480,12 +5438,12 @@
       <c r="L100" s="19"/>
       <c r="M100" s="19"/>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B100, $C$2:$C$895, C100, $D$2:$D$895, D100, $E$2:$E$895, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="19"/>
     </row>
-    <row r="101" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5518,12 +5476,12 @@
       <c r="L101" s="19"/>
       <c r="M101" s="19"/>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B101, $C$2:$C$895, C101, $D$2:$D$895, D101, $E$2:$E$895, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="19"/>
     </row>
-    <row r="102" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -5565,12 +5523,12 @@
         <v>300</v>
       </c>
       <c r="N102" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B102, $C$2:$C$895, C102, $D$2:$D$895, D102, $E$2:$E$895, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="20"/>
     </row>
-    <row r="103" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5603,12 +5561,12 @@
       <c r="L103" s="19"/>
       <c r="M103" s="19"/>
       <c r="N103" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B103, $C$2:$C$895, C103, $D$2:$D$895, D103, $E$2:$E$895, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="19"/>
     </row>
-    <row r="104" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="6" t="s">
         <v>62</v>
       </c>
@@ -5643,12 +5601,12 @@
       <c r="L104" s="19"/>
       <c r="M104" s="19"/>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B104, $C$2:$C$895, C104, $D$2:$D$895, D104, $E$2:$E$895, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="19"/>
     </row>
-    <row r="105" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="6" t="s">
         <v>62</v>
       </c>
@@ -5681,12 +5639,12 @@
       <c r="L105" s="19"/>
       <c r="M105" s="19"/>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B105, $C$2:$C$895, C105, $D$2:$D$895, D105, $E$2:$E$895, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="19"/>
     </row>
-    <row r="106" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="6" t="s">
         <v>62</v>
       </c>
@@ -5721,12 +5679,12 @@
       <c r="L106" s="19"/>
       <c r="M106" s="19"/>
       <c r="N106" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B106, $C$2:$C$895, C106, $D$2:$D$895, D106, $E$2:$E$895, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="19"/>
     </row>
-    <row r="107" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="6" t="s">
         <v>62</v>
       </c>
@@ -5759,12 +5717,12 @@
       <c r="L107" s="19"/>
       <c r="M107" s="19"/>
       <c r="N107" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B107, $C$2:$C$895, C107, $D$2:$D$895, D107, $E$2:$E$895, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="19"/>
     </row>
-    <row r="108" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5797,12 +5755,12 @@
       <c r="L108" s="19"/>
       <c r="M108" s="19"/>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B108, $C$2:$C$895, C108, $D$2:$D$895, D108, $E$2:$E$895, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="19"/>
     </row>
-    <row r="109" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="6" t="s">
         <v>62</v>
       </c>
@@ -5835,12 +5793,12 @@
       <c r="L109" s="19"/>
       <c r="M109" s="19"/>
       <c r="N109" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B109, $C$2:$C$895, C109, $D$2:$D$895, D109, $E$2:$E$895, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="19"/>
     </row>
-    <row r="110" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="6" t="s">
         <v>62</v>
       </c>
@@ -5875,12 +5833,12 @@
       <c r="L110" s="19"/>
       <c r="M110" s="19"/>
       <c r="N110" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B110, $C$2:$C$895, C110, $D$2:$D$895, D110, $E$2:$E$895, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="19"/>
     </row>
-    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="6" t="s">
         <v>62</v>
       </c>
@@ -5913,12 +5871,12 @@
       <c r="L111" s="19"/>
       <c r="M111" s="19"/>
       <c r="N111" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B111, $C$2:$C$895, C111, $D$2:$D$895, D111, $E$2:$E$895, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O111" s="19"/>
     </row>
-    <row r="112" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5951,12 +5909,12 @@
       <c r="L112" s="19"/>
       <c r="M112" s="19"/>
       <c r="N112" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B112, $C$2:$C$895, C112, $D$2:$D$895, D112, $E$2:$E$895, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="19"/>
     </row>
-    <row r="113" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="6" t="s">
         <v>62</v>
       </c>
@@ -5989,12 +5947,12 @@
       <c r="L113" s="19"/>
       <c r="M113" s="19"/>
       <c r="N113" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B113, $C$2:$C$895, C113, $D$2:$D$895, D113, $E$2:$E$895, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113" s="19"/>
     </row>
-    <row r="114" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="6" t="s">
         <v>62</v>
       </c>
@@ -6027,12 +5985,12 @@
       <c r="L114" s="19"/>
       <c r="M114" s="19"/>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B114, $C$2:$C$895, C114, $D$2:$D$895, D114, $E$2:$E$895, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114" s="19"/>
     </row>
-    <row r="115" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="3">
         <v>46252.6875</v>
       </c>
@@ -6067,12 +6025,12 @@
       <c r="L115" s="19"/>
       <c r="M115" s="19"/>
       <c r="N115" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B115, $C$2:$C$895, C115, $D$2:$D$895, D115, $E$2:$E$895, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="19"/>
     </row>
-    <row r="116" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="6" t="s">
         <v>62</v>
       </c>
@@ -6105,12 +6063,12 @@
       <c r="L116" s="19"/>
       <c r="M116" s="19"/>
       <c r="N116" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B116, $C$2:$C$895, C116, $D$2:$D$895, D116, $E$2:$E$895, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O116" s="19"/>
     </row>
-    <row r="117" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="6" t="s">
         <v>62</v>
       </c>
@@ -6143,12 +6101,12 @@
       <c r="L117" s="19"/>
       <c r="M117" s="19"/>
       <c r="N117" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B117, $C$2:$C$895, C117, $D$2:$D$895, D117, $E$2:$E$895, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="19"/>
     </row>
-    <row r="118" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="6" t="s">
         <v>62</v>
       </c>
@@ -6181,12 +6139,12 @@
       <c r="L118" s="19"/>
       <c r="M118" s="19"/>
       <c r="N118" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B118, $C$2:$C$895, C118, $D$2:$D$895, D118, $E$2:$E$895, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="19"/>
     </row>
-    <row r="119" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="3">
         <v>46254.375</v>
       </c>
@@ -6223,12 +6181,12 @@
       <c r="L119" s="19"/>
       <c r="M119" s="19"/>
       <c r="N119" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B119, $C$2:$C$895, C119, $D$2:$D$895, D119, $E$2:$E$895, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="19"/>
     </row>
-    <row r="120" spans="1:15" s="31" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:15" s="31" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="6" t="s">
         <v>62</v>
       </c>
@@ -6261,12 +6219,12 @@
       <c r="L120" s="19"/>
       <c r="M120" s="19"/>
       <c r="N120" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B120, $C$2:$C$895, C120, $D$2:$D$895, D120, $E$2:$E$895, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="19"/>
     </row>
-    <row r="121" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="6" t="s">
         <v>62</v>
       </c>
@@ -6299,12 +6257,12 @@
       <c r="L121" s="19"/>
       <c r="M121" s="19"/>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B121, $C$2:$C$895, C121, $D$2:$D$895, D121, $E$2:$E$895, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="19"/>
     </row>
-    <row r="122" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="6" t="s">
         <v>62</v>
       </c>
@@ -6337,12 +6295,12 @@
       <c r="L122" s="19"/>
       <c r="M122" s="19"/>
       <c r="N122" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B122, $C$2:$C$895, C122, $D$2:$D$895, D122, $E$2:$E$895, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="19"/>
     </row>
-    <row r="123" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="6" t="s">
         <v>62</v>
       </c>
@@ -6375,12 +6333,12 @@
       <c r="L123" s="19"/>
       <c r="M123" s="19"/>
       <c r="N123" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B123, $C$2:$C$895, C123, $D$2:$D$895, D123, $E$2:$E$895, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="19"/>
     </row>
-    <row r="124" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="6" t="s">
         <v>62</v>
       </c>
@@ -6413,12 +6371,12 @@
       <c r="L124" s="19"/>
       <c r="M124" s="19"/>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B124, $C$2:$C$895, C124, $D$2:$D$895, D124, $E$2:$E$895, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="19"/>
     </row>
-    <row r="125" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="6" t="s">
         <v>62</v>
       </c>
@@ -6451,12 +6409,12 @@
       <c r="L125" s="19"/>
       <c r="M125" s="19"/>
       <c r="N125" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B125, $C$2:$C$895, C125, $D$2:$D$895, D125, $E$2:$E$895, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="19"/>
     </row>
-    <row r="126" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="6" t="s">
         <v>62</v>
       </c>
@@ -6491,12 +6449,12 @@
       <c r="L126" s="19"/>
       <c r="M126" s="19"/>
       <c r="N126" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B126, $C$2:$C$895, C126, $D$2:$D$895, D126, $E$2:$E$895, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="19"/>
     </row>
-    <row r="127" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="3">
         <v>46252.6875</v>
       </c>
@@ -6529,12 +6487,12 @@
       <c r="L127" s="19"/>
       <c r="M127" s="19"/>
       <c r="N127" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B127, $C$2:$C$895, C127, $D$2:$D$895, D127, $E$2:$E$895, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="19"/>
     </row>
-    <row r="128" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="6" t="s">
         <v>62</v>
       </c>
@@ -6567,12 +6525,12 @@
       <c r="L128" s="19"/>
       <c r="M128" s="19"/>
       <c r="N128" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B128, $C$2:$C$895, C128, $D$2:$D$895, D128, $E$2:$E$895, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="19"/>
     </row>
-    <row r="129" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="6" t="s">
         <v>62</v>
       </c>
@@ -6605,12 +6563,12 @@
       <c r="L129" s="19"/>
       <c r="M129" s="19"/>
       <c r="N129" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B129, $C$2:$C$895, C129, $D$2:$D$895, D129, $E$2:$E$895, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="19"/>
     </row>
-    <row r="130" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="6" t="s">
         <v>62</v>
       </c>
@@ -6643,12 +6601,12 @@
       <c r="L130" s="19"/>
       <c r="M130" s="19"/>
       <c r="N130" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B130, $C$2:$C$895, C130, $D$2:$D$895, D130, $E$2:$E$895, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="2">IF(COUNTIFS( $B$2:$B$895, B130, $C$2:$C$895, C130, $D$2:$D$895, D130, $E$2:$E$895, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="19"/>
     </row>
-    <row r="131" spans="1:15" s="21" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:15" s="21" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="6" t="s">
         <v>62</v>
       </c>
@@ -6681,12 +6639,12 @@
       <c r="L131" s="19"/>
       <c r="M131" s="19"/>
       <c r="N131" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B131, $C$2:$C$895, C131, $D$2:$D$895, D131, $E$2:$E$895, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="19"/>
     </row>
-    <row r="132" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="6" t="s">
         <v>62</v>
       </c>
@@ -6721,12 +6679,12 @@
       <c r="L132" s="19"/>
       <c r="M132" s="19"/>
       <c r="N132" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B132, $C$2:$C$895, C132, $D$2:$D$895, D132, $E$2:$E$895, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="19"/>
     </row>
-    <row r="133" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="6" t="s">
         <v>62</v>
       </c>
@@ -6759,12 +6717,12 @@
       <c r="L133" s="19"/>
       <c r="M133" s="19"/>
       <c r="N133" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B133, $C$2:$C$895, C133, $D$2:$D$895, D133, $E$2:$E$895, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="19"/>
     </row>
-    <row r="134" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -6797,12 +6755,12 @@
       <c r="L134" s="19"/>
       <c r="M134" s="19"/>
       <c r="N134" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B134, $C$2:$C$895, C134, $D$2:$D$895, D134, $E$2:$E$895, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="19"/>
     </row>
-    <row r="135" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="6" t="s">
         <v>62</v>
       </c>
@@ -6835,12 +6793,12 @@
       <c r="L135" s="19"/>
       <c r="M135" s="19"/>
       <c r="N135" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B135, $C$2:$C$895, C135, $D$2:$D$895, D135, $E$2:$E$895, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="19"/>
     </row>
-    <row r="136" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="6" t="s">
         <v>62</v>
       </c>
@@ -6873,12 +6831,12 @@
       <c r="L136" s="19"/>
       <c r="M136" s="19"/>
       <c r="N136" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B136, $C$2:$C$895, C136, $D$2:$D$895, D136, $E$2:$E$895, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="19"/>
     </row>
-    <row r="137" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="6" t="s">
         <v>62</v>
       </c>
@@ -6913,12 +6871,12 @@
       <c r="L137" s="19"/>
       <c r="M137" s="19"/>
       <c r="N137" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B137, $C$2:$C$895, C137, $D$2:$D$895, D137, $E$2:$E$895, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="19"/>
     </row>
-    <row r="138" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="6" t="s">
         <v>62</v>
       </c>
@@ -6951,12 +6909,12 @@
       <c r="L138" s="19"/>
       <c r="M138" s="19"/>
       <c r="N138" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B138, $C$2:$C$895, C138, $D$2:$D$895, D138, $E$2:$E$895, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="19"/>
     </row>
-    <row r="139" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="6" t="s">
         <v>62</v>
       </c>
@@ -6989,12 +6947,12 @@
       <c r="L139" s="19"/>
       <c r="M139" s="19"/>
       <c r="N139" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B139, $C$2:$C$895, C139, $D$2:$D$895, D139, $E$2:$E$895, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="19"/>
     </row>
-    <row r="140" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="6" t="s">
         <v>62</v>
       </c>
@@ -7027,12 +6985,12 @@
       <c r="L140" s="19"/>
       <c r="M140" s="19"/>
       <c r="N140" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B140, $C$2:$C$895, C140, $D$2:$D$895, D140, $E$2:$E$895, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="19"/>
     </row>
-    <row r="141" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="6" t="s">
         <v>62</v>
       </c>
@@ -7065,12 +7023,12 @@
       <c r="L141" s="19"/>
       <c r="M141" s="19"/>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B141, $C$2:$C$895, C141, $D$2:$D$895, D141, $E$2:$E$895, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="19"/>
     </row>
-    <row r="142" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="6" t="s">
         <v>62</v>
       </c>
@@ -7105,11 +7063,11 @@
       <c r="L142" s="19"/>
       <c r="M142" s="19"/>
       <c r="N142" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B142, $C$2:$C$895, C142, $D$2:$D$895, D142, $E$2:$E$895, E142) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="143" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="143" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="6" t="s">
         <v>62</v>
       </c>
@@ -7142,12 +7100,12 @@
       <c r="L143" s="19"/>
       <c r="M143" s="19"/>
       <c r="N143" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B143, $C$2:$C$895, C143, $D$2:$D$895, D143, $E$2:$E$895, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="19"/>
     </row>
-    <row r="144" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="6" t="s">
         <v>62</v>
       </c>
@@ -7180,11 +7138,11 @@
       <c r="L144" s="19"/>
       <c r="M144" s="19"/>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B144, $C$2:$C$895, C144, $D$2:$D$895, D144, $E$2:$E$895, E144) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="145" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="145" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -7217,12 +7175,12 @@
       <c r="L145" s="19"/>
       <c r="M145" s="19"/>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B145, $C$2:$C$895, C145, $D$2:$D$895, D145, $E$2:$E$895, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O145" s="19"/>
     </row>
-    <row r="146" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="6" t="s">
         <v>62</v>
       </c>
@@ -7255,11 +7213,11 @@
       <c r="L146" s="19"/>
       <c r="M146" s="19"/>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B146, $C$2:$C$895, C146, $D$2:$D$895, D146, $E$2:$E$895, E146) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="147" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="147" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="6" t="s">
         <v>62</v>
       </c>
@@ -7292,12 +7250,12 @@
       <c r="L147" s="19"/>
       <c r="M147" s="19"/>
       <c r="N147" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B147, $C$2:$C$895, C147, $D$2:$D$895, D147, $E$2:$E$895, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="19"/>
     </row>
-    <row r="148" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="6" t="s">
         <v>62</v>
       </c>
@@ -7330,11 +7288,11 @@
       <c r="L148" s="19"/>
       <c r="M148" s="19"/>
       <c r="N148" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B148, $C$2:$C$895, C148, $D$2:$D$895, D148, $E$2:$E$895, E148) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="149" spans="1:15" ht="16.2" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -7371,11 +7329,11 @@
       <c r="L149" s="19"/>
       <c r="M149" s="19"/>
       <c r="N149" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B149, $C$2:$C$895, C149, $D$2:$D$895, D149, $E$2:$E$895, E149) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="150" spans="1:15" s="31" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="150" spans="1:15" s="31" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="3">
         <v>46261.375578703701</v>
       </c>
@@ -7417,12 +7375,12 @@
         <v>700</v>
       </c>
       <c r="N150" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B150, $C$2:$C$895, C150, $D$2:$D$895, D150, $E$2:$E$895, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="20"/>
     </row>
-    <row r="151" spans="1:15" ht="16.2" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="3">
         <v>46261.375613425924</v>
       </c>
@@ -7464,11 +7422,11 @@
         <v>300</v>
       </c>
       <c r="N151" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B151, $C$2:$C$895, C151, $D$2:$D$895, D151, $E$2:$E$895, E151) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="152" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="152" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -7510,11 +7468,11 @@
         <v>300</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B152, $C$2:$C$895, C152, $D$2:$D$895, D152, $E$2:$E$895, E152) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="153" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="153" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="13">
         <v>46252.6875</v>
       </c>
@@ -7546,11 +7504,11 @@
         <v>164</v>
       </c>
       <c r="N153" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B153, $C$2:$C$895, C153, $D$2:$D$895, D153, $E$2:$E$895, E153) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="154" spans="1:15" s="47" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="154" spans="1:15" s="47" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="3">
         <v>46261.375613425924</v>
       </c>
@@ -7592,12 +7550,12 @@
         <v>300</v>
       </c>
       <c r="N154" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B154, $C$2:$C$895, C154, $D$2:$D$895, D154, $E$2:$E$895, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="20"/>
     </row>
-    <row r="155" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="3">
         <v>46261.375810185185</v>
       </c>
@@ -7639,11 +7597,11 @@
         <v>300</v>
       </c>
       <c r="N155" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B155, $C$2:$C$895, C155, $D$2:$D$895, D155, $E$2:$E$895, E155) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="156" spans="1:15" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="156" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -7673,11 +7631,11 @@
       </c>
       <c r="J156" s="23"/>
       <c r="N156" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B156, $C$2:$C$895, C156, $D$2:$D$895, D156, $E$2:$E$895, E156) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="13">
         <v>46253.375</v>
       </c>
@@ -7712,11 +7670,11 @@
         <v>146</v>
       </c>
       <c r="N157" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B157, $C$2:$C$895, C157, $D$2:$D$895, D157, $E$2:$E$895, E157) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="13">
         <v>46252.6875</v>
       </c>
@@ -7746,11 +7704,11 @@
       </c>
       <c r="J158" s="23"/>
       <c r="N158" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B158, $C$2:$C$895, C158, $D$2:$D$895, D158, $E$2:$E$895, E158) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" ht="16.2" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="13">
         <v>46252.645833333336</v>
       </c>
@@ -7780,11 +7738,11 @@
       </c>
       <c r="J159" s="23"/>
       <c r="N159" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B159, $C$2:$C$895, C159, $D$2:$D$895, D159, $E$2:$E$895, E159) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="160" spans="1:15" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="33">
         <v>46260.634027777778</v>
       </c>
@@ -7826,14 +7784,14 @@
         <v>480</v>
       </c>
       <c r="N160" s="38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B160, $C$2:$C$895, C160, $D$2:$D$895, D160, $E$2:$E$895, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="37" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -7863,11 +7821,11 @@
       </c>
       <c r="J161" s="23"/>
       <c r="N161" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B161, $C$2:$C$895, C161, $D$2:$D$895, D161, $E$2:$E$895, E161) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="162" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="3">
         <v>46260.375</v>
       </c>
@@ -7909,11 +7867,11 @@
         <v>300</v>
       </c>
       <c r="N162" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B162, $C$2:$C$895, C162, $D$2:$D$895, D162, $E$2:$E$895, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="13">
         <v>46252.645833333336</v>
       </c>
@@ -7943,11 +7901,11 @@
       </c>
       <c r="J163" s="23"/>
       <c r="N163" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B163, $C$2:$C$895, C163, $D$2:$D$895, D163, $E$2:$E$895, E163) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="164" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -7977,11 +7935,11 @@
       </c>
       <c r="J164" s="23"/>
       <c r="N164" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B164, $C$2:$C$895, C164, $D$2:$D$895, D164, $E$2:$E$895, E164) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="165" spans="1:15" s="31" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" s="31" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="3">
         <v>46261.375613425924</v>
       </c>
@@ -8023,12 +7981,12 @@
         <v>300</v>
       </c>
       <c r="N165" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B165, $C$2:$C$895, C165, $D$2:$D$895, D165, $E$2:$E$895, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="20"/>
     </row>
-    <row r="166" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -8060,11 +8018,11 @@
         <v>41</v>
       </c>
       <c r="N166" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B166, $C$2:$C$895, C166, $D$2:$D$895, D166, $E$2:$E$895, E166) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="167" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -8096,11 +8054,11 @@
         <v>117</v>
       </c>
       <c r="N167" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B167, $C$2:$C$895, C167, $D$2:$D$895, D167, $E$2:$E$895, E167) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="168" spans="1:15" ht="16.2" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -8130,12 +8088,12 @@
       </c>
       <c r="J168" s="23"/>
       <c r="N168" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B168, $C$2:$C$895, C168, $D$2:$D$895, D168, $E$2:$E$895, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O168" s="12"/>
     </row>
-    <row r="169" spans="1:15" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="13">
         <v>46252.6875</v>
       </c>
@@ -8167,11 +8125,11 @@
         <v>55</v>
       </c>
       <c r="N169" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B169, $C$2:$C$895, C169, $D$2:$D$895, D169, $E$2:$E$895, E169) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="3">
         <v>46260.556944444441</v>
       </c>
@@ -8213,11 +8171,11 @@
         <v>150</v>
       </c>
       <c r="N170" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B170, $C$2:$C$895, C170, $D$2:$D$895, D170, $E$2:$E$895, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="171" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3">
         <v>46261.375613425924</v>
       </c>
@@ -8245,26 +8203,25 @@
       <c r="I171" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J171" s="72" t="s">
+      <c r="J171" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="K171" s="60" t="s">
+      <c r="K171" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="L171" s="60">
+      <c r="L171" s="20">
         <v>6005</v>
       </c>
-      <c r="M171" s="60">
+      <c r="M171" s="20">
         <f>ABS((D171*E171)-L171)</f>
         <v>250</v>
       </c>
-      <c r="N171" s="59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B171, $C$2:$C$895, C171, $D$2:$D$895, D171, $E$2:$E$895, E171) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N171" s="12" t="str">
+        <f t="shared" si="2"/>
         <v>Duplicate</v>
       </c>
-      <c r="O171" s="60"/>
-    </row>
-    <row r="172" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -8296,11 +8253,11 @@
         <v>41</v>
       </c>
       <c r="N172" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B172, $C$2:$C$895, C172, $D$2:$D$895, D172, $E$2:$E$895, E172) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3">
         <v>46261.48945601852</v>
       </c>
@@ -8342,11 +8299,11 @@
         <v>700</v>
       </c>
       <c r="N173" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B173, $C$2:$C$895, C173, $D$2:$D$895, D173, $E$2:$E$895, E173) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="174" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="13">
         <v>46252.6875</v>
       </c>
@@ -8378,11 +8335,11 @@
         <v>117</v>
       </c>
       <c r="N174" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B174, $C$2:$C$895, C174, $D$2:$D$895, D174, $E$2:$E$895, E174) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="3">
         <v>46261.375752314816</v>
       </c>
@@ -8424,11 +8381,11 @@
         <v>260</v>
       </c>
       <c r="N175" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B175, $C$2:$C$895, C175, $D$2:$D$895, D175, $E$2:$E$895, E175) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="176" spans="1:15" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -8470,11 +8427,11 @@
         <v>250</v>
       </c>
       <c r="N176" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B176, $C$2:$C$895, C176, $D$2:$D$895, D176, $E$2:$E$895, E176) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="177" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -8506,12 +8463,12 @@
         <v>118</v>
       </c>
       <c r="N177" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B177, $C$2:$C$895, C177, $D$2:$D$895, D177, $E$2:$E$895, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="12"/>
     </row>
-    <row r="178" spans="1:15" ht="15.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:15" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="3">
         <v>46261.615381944444</v>
       </c>
@@ -8553,11 +8510,11 @@
         <v>501</v>
       </c>
       <c r="N178" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B178, $C$2:$C$895, C178, $D$2:$D$895, D178, $E$2:$E$895, E178) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="10" t="s">
         <v>62</v>
       </c>
@@ -8589,12 +8546,12 @@
         <v>117</v>
       </c>
       <c r="N179" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B179, $C$2:$C$895, C179, $D$2:$D$895, D179, $E$2:$E$895, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="12"/>
     </row>
-    <row r="180" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="22">
         <v>46255</v>
       </c>
@@ -8636,11 +8593,11 @@
         <v>657</v>
       </c>
       <c r="N180" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B180, $C$2:$C$895, C180, $D$2:$D$895, D180, $E$2:$E$895, E180) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="181" spans="1:15" ht="15.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" ht="15.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="10" t="s">
         <v>62</v>
       </c>
@@ -8672,12 +8629,12 @@
         <v>117</v>
       </c>
       <c r="N181" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B181, $C$2:$C$895, C181, $D$2:$D$895, D181, $E$2:$E$895, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O181" s="12"/>
     </row>
-    <row r="182" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3">
         <v>46259.375</v>
       </c>
@@ -8719,11 +8676,11 @@
         <v>240</v>
       </c>
       <c r="N182" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B182, $C$2:$C$895, C182, $D$2:$D$895, D182, $E$2:$E$895, E182) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="183" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -8753,12 +8710,12 @@
       </c>
       <c r="J183" s="23"/>
       <c r="N183" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B183, $C$2:$C$895, C183, $D$2:$D$895, D183, $E$2:$E$895, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="12"/>
     </row>
-    <row r="184" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="10" t="s">
         <v>62</v>
       </c>
@@ -8790,11 +8747,11 @@
         <v>118</v>
       </c>
       <c r="N184" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B184, $C$2:$C$895, C184, $D$2:$D$895, D184, $E$2:$E$895, E184) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="185" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="10" t="s">
         <v>62</v>
       </c>
@@ -8826,12 +8783,12 @@
         <v>118</v>
       </c>
       <c r="N185" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B185, $C$2:$C$895, C185, $D$2:$D$895, D185, $E$2:$E$895, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="12"/>
     </row>
-    <row r="186" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="3">
         <v>46260.375</v>
       </c>
@@ -8873,11 +8830,11 @@
         <v>800</v>
       </c>
       <c r="N186" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B186, $C$2:$C$895, C186, $D$2:$D$895, D186, $E$2:$E$895, E186) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="3">
         <v>46258.443749999999</v>
       </c>
@@ -8919,11 +8876,11 @@
         <v>527.5</v>
       </c>
       <c r="N187" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B187, $C$2:$C$895, C187, $D$2:$D$895, D187, $E$2:$E$895, E187) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" s="31" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" s="31" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="13">
         <v>46253.4</v>
       </c>
@@ -8960,12 +8917,12 @@
       <c r="L188" s="20"/>
       <c r="M188" s="20"/>
       <c r="N188" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B188, $C$2:$C$895, C188, $D$2:$D$895, D188, $E$2:$E$895, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O188" s="20"/>
     </row>
-    <row r="189" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -8997,11 +8954,11 @@
         <v>118</v>
       </c>
       <c r="N189" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B189, $C$2:$C$895, C189, $D$2:$D$895, D189, $E$2:$E$895, E189) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="190" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="6" t="s">
         <v>62</v>
       </c>
@@ -9036,11 +8993,11 @@
       <c r="L190" s="19"/>
       <c r="M190" s="19"/>
       <c r="N190" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B190, $C$2:$C$895, C190, $D$2:$D$895, D190, $E$2:$E$895, E190) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="191" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="10" t="s">
         <v>62</v>
       </c>
@@ -9070,11 +9027,11 @@
       </c>
       <c r="J191" s="23"/>
       <c r="N191" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B191, $C$2:$C$895, C191, $D$2:$D$895, D191, $E$2:$E$895, E191) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="13">
         <v>46252.6875</v>
       </c>
@@ -9102,19 +9059,19 @@
       <c r="I192" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J192" s="75" t="s">
+      <c r="J192" s="32" t="s">
         <v>41</v>
       </c>
       <c r="K192" s="20"/>
       <c r="L192" s="20"/>
       <c r="M192" s="20"/>
       <c r="N192" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B192, $C$2:$C$895, C192, $D$2:$D$895, D192, $E$2:$E$895, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="12"/>
     </row>
-    <row r="193" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="10" t="s">
         <v>62</v>
       </c>
@@ -9142,17 +9099,17 @@
       <c r="I193" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J193" s="75"/>
+      <c r="J193" s="32"/>
       <c r="K193" s="20"/>
       <c r="L193" s="20"/>
       <c r="M193" s="20"/>
       <c r="N193" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B193, $C$2:$C$895, C193, $D$2:$D$895, D193, $E$2:$E$895, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="2"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="12"/>
     </row>
-    <row r="194" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -9180,7 +9137,7 @@
       <c r="I194" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J194" s="76" t="s">
+      <c r="J194" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K194" s="20" t="s">
@@ -9194,12 +9151,12 @@
         <v>300</v>
       </c>
       <c r="N194" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B194, $C$2:$C$895, C194, $D$2:$D$895, D194, $E$2:$E$895, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="3">IF(COUNTIFS( $B$2:$B$895, B194, $C$2:$C$895, C194, $D$2:$D$895, D194, $E$2:$E$895, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="20"/>
     </row>
-    <row r="195" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="3">
         <v>46259.375</v>
       </c>
@@ -9227,7 +9184,7 @@
       <c r="I195" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J195" s="76" t="s">
+      <c r="J195" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K195" s="20" t="s">
@@ -9241,12 +9198,12 @@
         <v>188</v>
       </c>
       <c r="N195" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B195, $C$2:$C$895, C195, $D$2:$D$895, D195, $E$2:$E$895, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="20"/>
     </row>
-    <row r="196" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -9274,19 +9231,19 @@
       <c r="I196" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J196" s="75" t="s">
+      <c r="J196" s="32" t="s">
         <v>118</v>
       </c>
       <c r="K196" s="20"/>
       <c r="L196" s="20"/>
       <c r="M196" s="20"/>
       <c r="N196" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B196, $C$2:$C$895, C196, $D$2:$D$895, D196, $E$2:$E$895, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="12"/>
     </row>
-    <row r="197" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -9314,17 +9271,17 @@
       <c r="I197" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J197" s="75"/>
+      <c r="J197" s="32"/>
       <c r="K197" s="20"/>
       <c r="L197" s="20"/>
       <c r="M197" s="20"/>
       <c r="N197" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B197, $C$2:$C$895, C197, $D$2:$D$895, D197, $E$2:$E$895, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="12"/>
     </row>
-    <row r="198" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="33">
         <v>46259.375</v>
       </c>
@@ -9352,7 +9309,7 @@
       <c r="I198" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J198" s="73" t="s">
+      <c r="J198" s="61" t="s">
         <v>118</v>
       </c>
       <c r="K198" s="37" t="s">
@@ -9366,14 +9323,14 @@
         <v>650</v>
       </c>
       <c r="N198" s="31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B198, $C$2:$C$895, C198, $D$2:$D$895, D198, $E$2:$E$895, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="37" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="199" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:15" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -9401,7 +9358,7 @@
       <c r="I199" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J199" s="76" t="s">
+      <c r="J199" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K199" s="20" t="s">
@@ -9415,12 +9372,12 @@
         <v>250</v>
       </c>
       <c r="N199" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B199, $C$2:$C$895, C199, $D$2:$D$895, D199, $E$2:$E$895, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="20"/>
     </row>
-    <row r="200" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="39">
         <v>46260.425694444442</v>
       </c>
@@ -9448,7 +9405,7 @@
       <c r="I200" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J200" s="77" t="s">
+      <c r="J200" s="45" t="s">
         <v>118</v>
       </c>
       <c r="K200" s="45" t="s">
@@ -9462,12 +9419,12 @@
         <v>1000</v>
       </c>
       <c r="N200" s="46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B200, $C$2:$C$895, C200, $D$2:$D$895, D200, $E$2:$E$895, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O200" s="45"/>
     </row>
-    <row r="201" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="22">
         <v>46255</v>
       </c>
@@ -9509,11 +9466,11 @@
         <v>140</v>
       </c>
       <c r="N201" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B201, $C$2:$C$895, C201, $D$2:$D$895, D201, $E$2:$E$895, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="202" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="3">
         <v>46261.385555555556</v>
       </c>
@@ -9541,26 +9498,25 @@
       <c r="I202" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J202" s="60" t="s">
+      <c r="J202" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="K202" s="60" t="s">
+      <c r="K202" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="L202" s="60">
+      <c r="L202" s="20">
         <v>4520</v>
       </c>
-      <c r="M202" s="60">
+      <c r="M202" s="20">
         <f>ABS((D202*E202)-L202)</f>
         <v>300</v>
       </c>
-      <c r="N202" s="59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B202, $C$2:$C$895, C202, $D$2:$D$895, D202, $E$2:$E$895, E202) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N202" s="12" t="str">
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
-      <c r="O202" s="60"/>
-    </row>
-    <row r="203" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="10" t="s">
         <v>62</v>
       </c>
@@ -9588,16 +9544,16 @@
       <c r="I203" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J203" s="75" t="s">
+      <c r="J203" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N203" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B203, $C$2:$C$895, C203, $D$2:$D$895, D203, $E$2:$E$895, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="12"/>
     </row>
-    <row r="204" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="10" t="s">
         <v>62</v>
       </c>
@@ -9625,15 +9581,15 @@
       <c r="I204" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J204" s="75" t="s">
+      <c r="J204" s="32" t="s">
         <v>55</v>
       </c>
       <c r="N204" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B204, $C$2:$C$895, C204, $D$2:$D$895, D204, $E$2:$E$895, E204) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -9661,15 +9617,15 @@
       <c r="I205" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J205" s="71" t="s">
+      <c r="J205" s="19" t="s">
         <v>117</v>
       </c>
       <c r="N205" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B205, $C$2:$C$895, C205, $D$2:$D$895, D205, $E$2:$E$895, E205) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="206" spans="1:15" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" s="21" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="10" t="s">
         <v>62</v>
       </c>
@@ -9697,17 +9653,17 @@
       <c r="I206" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J206" s="75"/>
+      <c r="J206" s="32"/>
       <c r="K206" s="20"/>
       <c r="L206" s="20"/>
       <c r="M206" s="20"/>
       <c r="N206" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B206, $C$2:$C$895, C206, $D$2:$D$895, D206, $E$2:$E$895, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="12"/>
     </row>
-    <row r="207" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -9735,14 +9691,14 @@
       <c r="I207" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J207" s="75"/>
+      <c r="J207" s="32"/>
       <c r="N207" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B207, $C$2:$C$895, C207, $D$2:$D$895, D207, $E$2:$E$895, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="12"/>
     </row>
-    <row r="208" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="10" t="s">
         <v>62</v>
       </c>
@@ -9774,12 +9730,12 @@
         <v>118</v>
       </c>
       <c r="N208" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B208, $C$2:$C$895, C208, $D$2:$D$895, D208, $E$2:$E$895, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="12"/>
     </row>
-    <row r="209" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -9807,7 +9763,7 @@
       <c r="I209" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J209" s="76" t="s">
+      <c r="J209" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K209" s="20" t="s">
@@ -9821,11 +9777,11 @@
         <v>300</v>
       </c>
       <c r="N209" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B209, $C$2:$C$895, C209, $D$2:$D$895, D209, $E$2:$E$895, E209) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="210" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -9853,7 +9809,7 @@
       <c r="I210" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J210" s="76" t="s">
+      <c r="J210" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K210" s="20" t="s">
@@ -9867,11 +9823,11 @@
         <v>940</v>
       </c>
       <c r="N210" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B210, $C$2:$C$895, C210, $D$2:$D$895, D210, $E$2:$E$895, E210) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="211" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="10" t="s">
         <v>62</v>
       </c>
@@ -9903,12 +9859,12 @@
         <v>118</v>
       </c>
       <c r="N211" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B211, $C$2:$C$895, C211, $D$2:$D$895, D211, $E$2:$E$895, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O211" s="12"/>
     </row>
-    <row r="212" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="10" t="s">
         <v>62</v>
       </c>
@@ -9938,12 +9894,12 @@
       </c>
       <c r="J212" s="32"/>
       <c r="N212" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B212, $C$2:$C$895, C212, $D$2:$D$895, D212, $E$2:$E$895, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="12"/>
     </row>
-    <row r="213" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="3">
         <v>46261.375613425924</v>
       </c>
@@ -9985,11 +9941,11 @@
         <v>260</v>
       </c>
       <c r="N213" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B213, $C$2:$C$895, C213, $D$2:$D$895, D213, $E$2:$E$895, E213) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="214" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="10" t="s">
         <v>62</v>
       </c>
@@ -10019,12 +9975,12 @@
       </c>
       <c r="J214" s="32"/>
       <c r="N214" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B214, $C$2:$C$895, C214, $D$2:$D$895, D214, $E$2:$E$895, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="12"/>
     </row>
-    <row r="215" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="10" t="s">
         <v>62</v>
       </c>
@@ -10052,14 +10008,14 @@
       <c r="I215" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J215" s="75"/>
+      <c r="J215" s="32"/>
       <c r="N215" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B215, $C$2:$C$895, C215, $D$2:$D$895, D215, $E$2:$E$895, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="12"/>
     </row>
-    <row r="216" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -10101,11 +10057,11 @@
         <v>500</v>
       </c>
       <c r="N216" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B216, $C$2:$C$895, C216, $D$2:$D$895, D216, $E$2:$E$895, E216) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="217" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="10" t="s">
         <v>62</v>
       </c>
@@ -10135,12 +10091,12 @@
       </c>
       <c r="J217" s="32"/>
       <c r="N217" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B217, $C$2:$C$895, C217, $D$2:$D$895, D217, $E$2:$E$895, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O217" s="12"/>
     </row>
-    <row r="218" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="10" t="s">
         <v>62</v>
       </c>
@@ -10172,12 +10128,12 @@
         <v>118</v>
       </c>
       <c r="N218" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B218, $C$2:$C$895, C218, $D$2:$D$895, D218, $E$2:$E$895, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O218" s="12"/>
     </row>
-    <row r="219" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -10207,12 +10163,12 @@
       </c>
       <c r="J219" s="32"/>
       <c r="N219" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B219, $C$2:$C$895, C219, $D$2:$D$895, D219, $E$2:$E$895, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="12"/>
     </row>
-    <row r="220" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -10240,15 +10196,15 @@
       <c r="I220" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J220" s="74" t="s">
+      <c r="J220" s="62" t="s">
         <v>55</v>
       </c>
       <c r="N220" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B220, $C$2:$C$895, C220, $D$2:$D$895, D220, $E$2:$E$895, E220) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="221" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="10" t="s">
         <v>62</v>
       </c>
@@ -10280,12 +10236,12 @@
         <v>118</v>
       </c>
       <c r="N221" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B221, $C$2:$C$895, C221, $D$2:$D$895, D221, $E$2:$E$895, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="12"/>
     </row>
-    <row r="222" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="10" t="s">
         <v>62</v>
       </c>
@@ -10315,12 +10271,12 @@
       </c>
       <c r="J222" s="32"/>
       <c r="N222" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B222, $C$2:$C$895, C222, $D$2:$D$895, D222, $E$2:$E$895, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="12"/>
     </row>
-    <row r="223" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="10" t="s">
         <v>62</v>
       </c>
@@ -10350,12 +10306,12 @@
       </c>
       <c r="J223" s="32"/>
       <c r="N223" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B223, $C$2:$C$895, C223, $D$2:$D$895, D223, $E$2:$E$895, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="12"/>
     </row>
-    <row r="224" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -10387,12 +10343,12 @@
         <v>118</v>
       </c>
       <c r="N224" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B224, $C$2:$C$895, C224, $D$2:$D$895, D224, $E$2:$E$895, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="12"/>
     </row>
-    <row r="225" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="10" t="s">
         <v>62</v>
       </c>
@@ -10424,12 +10380,12 @@
         <v>117</v>
       </c>
       <c r="N225" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B225, $C$2:$C$895, C225, $D$2:$D$895, D225, $E$2:$E$895, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="12"/>
     </row>
-    <row r="226" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="13">
         <v>46253.375</v>
       </c>
@@ -10462,12 +10418,12 @@
         <v>145</v>
       </c>
       <c r="N226" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B226, $C$2:$C$895, C226, $D$2:$D$895, D226, $E$2:$E$895, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="12"/>
     </row>
-    <row r="227" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -10499,12 +10455,12 @@
         <v>55</v>
       </c>
       <c r="N227" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B227, $C$2:$C$895, C227, $D$2:$D$895, D227, $E$2:$E$895, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="12"/>
     </row>
-    <row r="228" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -10539,11 +10495,11 @@
         <v>147</v>
       </c>
       <c r="N228" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B228, $C$2:$C$895, C228, $D$2:$D$895, D228, $E$2:$E$895, E228) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="229" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="10" t="s">
         <v>62</v>
       </c>
@@ -10571,14 +10527,14 @@
       <c r="I229" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J229" s="75"/>
+      <c r="J229" s="32"/>
       <c r="N229" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B229, $C$2:$C$895, C229, $D$2:$D$895, D229, $E$2:$E$895, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="12"/>
     </row>
-    <row r="230" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="3">
         <v>46260.375</v>
       </c>
@@ -10606,7 +10562,7 @@
       <c r="I230" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J230" s="76" t="s">
+      <c r="J230" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K230" s="20" t="s">
@@ -10620,11 +10576,11 @@
         <v>650</v>
       </c>
       <c r="N230" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B230, $C$2:$C$895, C230, $D$2:$D$895, D230, $E$2:$E$895, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="10" t="s">
         <v>62</v>
       </c>
@@ -10652,13 +10608,13 @@
       <c r="I231" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J231" s="75"/>
+      <c r="J231" s="32"/>
       <c r="N231" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B231, $C$2:$C$895, C231, $D$2:$D$895, D231, $E$2:$E$895, E231) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="232" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="10" t="s">
         <v>62</v>
       </c>
@@ -10686,14 +10642,14 @@
       <c r="I232" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J232" s="75"/>
+      <c r="J232" s="32"/>
       <c r="N232" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B232, $C$2:$C$895, C232, $D$2:$D$895, D232, $E$2:$E$895, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="12"/>
     </row>
-    <row r="233" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -10721,15 +10677,15 @@
       <c r="I233" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J233" s="75" t="s">
+      <c r="J233" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N233" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B233, $C$2:$C$895, C233, $D$2:$D$895, D233, $E$2:$E$895, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="10" t="s">
         <v>62</v>
       </c>
@@ -10757,14 +10713,14 @@
       <c r="I234" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J234" s="75"/>
+      <c r="J234" s="32"/>
       <c r="N234" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B234, $C$2:$C$895, C234, $D$2:$D$895, D234, $E$2:$E$895, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O234" s="12"/>
     </row>
-    <row r="235" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="10" t="s">
         <v>62</v>
       </c>
@@ -10792,16 +10748,16 @@
       <c r="I235" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J235" s="75" t="s">
+      <c r="J235" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N235" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B235, $C$2:$C$895, C235, $D$2:$D$895, D235, $E$2:$E$895, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="12"/>
     </row>
-    <row r="236" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="10" t="s">
         <v>62</v>
       </c>
@@ -10829,14 +10785,14 @@
       <c r="I236" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J236" s="75"/>
+      <c r="J236" s="32"/>
       <c r="N236" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B236, $C$2:$C$895, C236, $D$2:$D$895, D236, $E$2:$E$895, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="12"/>
     </row>
-    <row r="237" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="10" t="s">
         <v>62</v>
       </c>
@@ -10864,16 +10820,16 @@
       <c r="I237" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J237" s="75" t="s">
+      <c r="J237" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N237" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B237, $C$2:$C$895, C237, $D$2:$D$895, D237, $E$2:$E$895, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O237" s="12"/>
     </row>
-    <row r="238" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="10" t="s">
         <v>62</v>
       </c>
@@ -10901,13 +10857,13 @@
       <c r="I238" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J238" s="75"/>
+      <c r="J238" s="32"/>
       <c r="N238" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B238, $C$2:$C$895, C238, $D$2:$D$895, D238, $E$2:$E$895, E238) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="239" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="13">
         <v>46252.6875</v>
       </c>
@@ -10935,16 +10891,16 @@
       <c r="I239" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J239" s="75" t="s">
+      <c r="J239" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N239" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B239, $C$2:$C$895, C239, $D$2:$D$895, D239, $E$2:$E$895, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="12"/>
     </row>
-    <row r="240" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="10" t="s">
         <v>62</v>
       </c>
@@ -10972,14 +10928,14 @@
       <c r="I240" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J240" s="75"/>
+      <c r="J240" s="32"/>
       <c r="N240" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B240, $C$2:$C$895, C240, $D$2:$D$895, D240, $E$2:$E$895, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="12"/>
     </row>
-    <row r="241" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="10" t="s">
         <v>62</v>
       </c>
@@ -11007,14 +10963,14 @@
       <c r="I241" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J241" s="75"/>
+      <c r="J241" s="32"/>
       <c r="N241" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B241, $C$2:$C$895, C241, $D$2:$D$895, D241, $E$2:$E$895, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="12"/>
     </row>
-    <row r="242" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="10" t="s">
         <v>62</v>
       </c>
@@ -11042,14 +10998,14 @@
       <c r="I242" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J242" s="75"/>
+      <c r="J242" s="32"/>
       <c r="N242" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B242, $C$2:$C$895, C242, $D$2:$D$895, D242, $E$2:$E$895, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="12"/>
     </row>
-    <row r="243" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="10" t="s">
         <v>62</v>
       </c>
@@ -11077,16 +11033,16 @@
       <c r="I243" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J243" s="75" t="s">
+      <c r="J243" s="32" t="s">
         <v>117</v>
       </c>
       <c r="N243" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B243, $C$2:$C$895, C243, $D$2:$D$895, D243, $E$2:$E$895, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="12"/>
     </row>
-    <row r="244" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="22">
         <v>46255</v>
       </c>
@@ -11114,7 +11070,7 @@
       <c r="I244" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J244" s="76" t="s">
+      <c r="J244" s="20" t="s">
         <v>55</v>
       </c>
       <c r="K244" s="20" t="s">
@@ -11128,11 +11084,11 @@
         <v>300</v>
       </c>
       <c r="N244" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B244, $C$2:$C$895, C244, $D$2:$D$895, D244, $E$2:$E$895, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="10" t="s">
         <v>62</v>
       </c>
@@ -11160,14 +11116,14 @@
       <c r="I245" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J245" s="75"/>
+      <c r="J245" s="32"/>
       <c r="N245" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B245, $C$2:$C$895, C245, $D$2:$D$895, D245, $E$2:$E$895, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="12"/>
     </row>
-    <row r="246" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="10" t="s">
         <v>62</v>
       </c>
@@ -11195,16 +11151,16 @@
       <c r="I246" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J246" s="75" t="s">
+      <c r="J246" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N246" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B246, $C$2:$C$895, C246, $D$2:$D$895, D246, $E$2:$E$895, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="12"/>
     </row>
-    <row r="247" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="10" t="s">
         <v>62</v>
       </c>
@@ -11232,14 +11188,14 @@
       <c r="I247" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J247" s="75"/>
+      <c r="J247" s="32"/>
       <c r="N247" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B247, $C$2:$C$895, C247, $D$2:$D$895, D247, $E$2:$E$895, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="12"/>
     </row>
-    <row r="248" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="10" t="s">
         <v>62</v>
       </c>
@@ -11267,14 +11223,14 @@
       <c r="I248" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J248" s="75"/>
+      <c r="J248" s="32"/>
       <c r="N248" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B248, $C$2:$C$895, C248, $D$2:$D$895, D248, $E$2:$E$895, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O248" s="12"/>
     </row>
-    <row r="249" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="10" t="s">
         <v>62</v>
       </c>
@@ -11302,14 +11258,14 @@
       <c r="I249" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J249" s="75"/>
+      <c r="J249" s="32"/>
       <c r="N249" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B249, $C$2:$C$895, C249, $D$2:$D$895, D249, $E$2:$E$895, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="12"/>
     </row>
-    <row r="250" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="10" t="s">
         <v>62</v>
       </c>
@@ -11337,16 +11293,16 @@
       <c r="I250" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J250" s="75" t="s">
+      <c r="J250" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N250" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B250, $C$2:$C$895, C250, $D$2:$D$895, D250, $E$2:$E$895, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="19"/>
     </row>
-    <row r="251" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="10" t="s">
         <v>62</v>
       </c>
@@ -11374,13 +11330,13 @@
       <c r="I251" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J251" s="75"/>
+      <c r="J251" s="32"/>
       <c r="N251" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B251, $C$2:$C$895, C251, $D$2:$D$895, D251, $E$2:$E$895, E251) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="252" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -11408,7 +11364,7 @@
       <c r="I252" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J252" s="76" t="s">
+      <c r="J252" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K252" s="20" t="s">
@@ -11422,11 +11378,11 @@
         <v>250</v>
       </c>
       <c r="N252" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B252, $C$2:$C$895, C252, $D$2:$D$895, D252, $E$2:$E$895, E252) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="253" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A253" s="10" t="s">
         <v>62</v>
       </c>
@@ -11454,14 +11410,14 @@
       <c r="I253" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J253" s="75"/>
+      <c r="J253" s="32"/>
       <c r="N253" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B253, $C$2:$C$895, C253, $D$2:$D$895, D253, $E$2:$E$895, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="19"/>
     </row>
-    <row r="254" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="10" t="s">
         <v>62</v>
       </c>
@@ -11489,14 +11445,14 @@
       <c r="I254" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J254" s="75"/>
+      <c r="J254" s="32"/>
       <c r="N254" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B254, $C$2:$C$895, C254, $D$2:$D$895, D254, $E$2:$E$895, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="12"/>
     </row>
-    <row r="255" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A255" s="10" t="s">
         <v>62</v>
       </c>
@@ -11524,14 +11480,14 @@
       <c r="I255" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J255" s="75"/>
+      <c r="J255" s="32"/>
       <c r="N255" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B255, $C$2:$C$895, C255, $D$2:$D$895, D255, $E$2:$E$895, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O255" s="12"/>
     </row>
-    <row r="256" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A256" s="10" t="s">
         <v>62</v>
       </c>
@@ -11559,15 +11515,15 @@
       <c r="I256" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J256" s="75" t="s">
+      <c r="J256" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N256" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B256, $C$2:$C$895, C256, $D$2:$D$895, D256, $E$2:$E$895, E256) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="257" spans="1:15" s="59" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="257" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A257" s="10" t="s">
         <v>62</v>
       </c>
@@ -11595,17 +11551,14 @@
       <c r="I257" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J257" s="75"/>
-      <c r="K257" s="20"/>
-      <c r="L257" s="20"/>
-      <c r="M257" s="20"/>
+      <c r="J257" s="32"/>
       <c r="N257" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B257, $C$2:$C$895, C257, $D$2:$D$895, D257, $E$2:$E$895, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="12"/>
     </row>
-    <row r="258" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A258" s="13">
         <v>46252.6875</v>
       </c>
@@ -11633,15 +11586,15 @@
       <c r="I258" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J258" s="75" t="s">
+      <c r="J258" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N258" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B258, $C$2:$C$895, C258, $D$2:$D$895, D258, $E$2:$E$895, E258) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="259" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="N258:N270" si="4">IF(COUNTIFS( $B$2:$B$895, B258, $C$2:$C$895, C258, $D$2:$D$895, D258, $E$2:$E$895, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="259" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A259" s="11" t="s">
         <v>62</v>
       </c>
@@ -11669,14 +11622,14 @@
       <c r="I259" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J259" s="75"/>
+      <c r="J259" s="32"/>
       <c r="N259" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B259, $C$2:$C$895, C259, $D$2:$D$895, D259, $E$2:$E$895, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="19"/>
     </row>
-    <row r="260" spans="1:15" s="59" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A260" s="10" t="s">
         <v>62</v>
       </c>
@@ -11704,17 +11657,14 @@
       <c r="I260" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J260" s="75"/>
-      <c r="K260" s="20"/>
-      <c r="L260" s="20"/>
-      <c r="M260" s="20"/>
+      <c r="J260" s="32"/>
       <c r="N260" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B260, $C$2:$C$895, C260, $D$2:$D$895, D260, $E$2:$E$895, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="12"/>
     </row>
-    <row r="261" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A261" s="10" t="s">
         <v>62</v>
       </c>
@@ -11742,13 +11692,13 @@
       <c r="I261" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J261" s="75"/>
+      <c r="J261" s="32"/>
       <c r="N261" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B261, $C$2:$C$895, C261, $D$2:$D$895, D261, $E$2:$E$895, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A262" s="10" t="s">
         <v>62</v>
       </c>
@@ -11776,13 +11726,13 @@
       <c r="I262" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J262" s="75"/>
+      <c r="J262" s="32"/>
       <c r="N262" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B262, $C$2:$C$895, C262, $D$2:$D$895, D262, $E$2:$E$895, E262) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="263" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="263" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A263" s="10" t="s">
         <v>62</v>
       </c>
@@ -11810,14 +11760,14 @@
       <c r="I263" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J263" s="75"/>
+      <c r="J263" s="32"/>
       <c r="N263" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B263, $C$2:$C$895, C263, $D$2:$D$895, D263, $E$2:$E$895, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="12"/>
     </row>
-    <row r="264" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A264" s="10" t="s">
         <v>62</v>
       </c>
@@ -11845,16 +11795,16 @@
       <c r="I264" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J264" s="75" t="s">
+      <c r="J264" s="32" t="s">
         <v>118</v>
       </c>
       <c r="N264" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B264, $C$2:$C$895, C264, $D$2:$D$895, D264, $E$2:$E$895, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="19"/>
     </row>
-    <row r="265" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A265" s="10" t="s">
         <v>62</v>
       </c>
@@ -11882,14 +11832,14 @@
       <c r="I265" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J265" s="75"/>
+      <c r="J265" s="32"/>
       <c r="N265" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B265, $C$2:$C$895, C265, $D$2:$D$895, D265, $E$2:$E$895, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="19"/>
     </row>
-    <row r="266" spans="1:15" s="59" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="10" t="s">
         <v>62</v>
       </c>
@@ -11917,17 +11867,14 @@
       <c r="I266" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J266" s="75"/>
-      <c r="K266" s="20"/>
-      <c r="L266" s="20"/>
-      <c r="M266" s="20"/>
+      <c r="J266" s="32"/>
       <c r="N266" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B266, $C$2:$C$895, C266, $D$2:$D$895, D266, $E$2:$E$895, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="19"/>
     </row>
-    <row r="267" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -11955,7 +11902,7 @@
       <c r="I267" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J267" s="75" t="s">
+      <c r="J267" s="32" t="s">
         <v>118</v>
       </c>
       <c r="K267" s="20" t="s">
@@ -11969,11 +11916,11 @@
         <v>250</v>
       </c>
       <c r="N267" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B267, $C$2:$C$895, C267, $D$2:$D$895, D267, $E$2:$E$895, E267) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="268" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="268" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A268" s="10" t="s">
         <v>62</v>
       </c>
@@ -12001,14 +11948,14 @@
       <c r="I268" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J268" s="75"/>
+      <c r="J268" s="32"/>
       <c r="N268" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B268, $C$2:$C$895, C268, $D$2:$D$895, D268, $E$2:$E$895, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="19"/>
     </row>
-    <row r="269" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="13">
         <v>46251.506249999999</v>
       </c>
@@ -12036,14 +11983,14 @@
       <c r="I269" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J269" s="75"/>
+      <c r="J269" s="32"/>
       <c r="N269" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B269, $C$2:$C$895, C269, $D$2:$D$895, D269, $E$2:$E$895, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="19"/>
     </row>
-    <row r="270" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A270" s="10" t="s">
         <v>62</v>
       </c>
@@ -12071,21 +12018,26 @@
       <c r="I270" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J270" s="75"/>
+      <c r="J270" s="32"/>
       <c r="N270" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$895, B270, $C$2:$C$895, C270, $D$2:$D$895, D270, $E$2:$E$895, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O270" s="19"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O270">
+  <autoFilter ref="A1:O270" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="COCHINSHIPEQ"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="2">
       <filters>
         <filter val="B"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:O190">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O190">
       <sortCondition descending="1" ref="F1:F270"/>
     </sortState>
   </autoFilter>
@@ -12095,15 +12047,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.109375" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" customWidth="1"/>
+    <col min="1" max="1" width="27.08984375" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -12123,7 +12075,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>197</v>
       </c>
@@ -12155,7 +12107,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>198</v>
       </c>
@@ -12187,7 +12139,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>199</v>
       </c>
@@ -12219,7 +12171,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>199</v>
       </c>
@@ -12251,7 +12203,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>200</v>
       </c>
@@ -12283,7 +12235,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>201</v>
       </c>
@@ -12315,7 +12267,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>202</v>
       </c>
@@ -12347,7 +12299,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>203</v>
       </c>
@@ -12379,7 +12331,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>204</v>
       </c>
@@ -12411,7 +12363,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>205</v>
       </c>
@@ -12443,7 +12395,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>204</v>
       </c>
@@ -12475,7 +12427,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>204</v>
       </c>
@@ -12507,7 +12459,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>204</v>
       </c>
@@ -12539,7 +12491,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>204</v>
       </c>
@@ -12571,7 +12523,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>206</v>
       </c>
@@ -12603,7 +12555,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>207</v>
       </c>
@@ -12635,7 +12587,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>207</v>
       </c>
@@ -12667,7 +12619,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>208</v>
       </c>
@@ -12699,7 +12651,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>207</v>
       </c>
@@ -12737,27 +12689,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O271"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.109375" style="12" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="12"/>
-    <col min="4" max="5" width="8.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="8.77734375" style="12"/>
-    <col min="10" max="10" width="10.5546875" style="20" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="8.81640625" style="12"/>
+    <col min="4" max="5" width="8.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.1796875" style="12" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="12" customWidth="1"/>
+    <col min="9" max="9" width="8.81640625" style="12"/>
+    <col min="10" max="10" width="10.54296875" style="20" customWidth="1"/>
     <col min="11" max="11" width="19" style="20" customWidth="1"/>
-    <col min="12" max="13" width="8.88671875" style="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="12"/>
-    <col min="15" max="15" width="8.77734375" style="20"/>
-    <col min="16" max="16384" width="8.77734375" style="12"/>
+    <col min="12" max="13" width="8.90625" style="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.81640625" style="12"/>
+    <col min="15" max="15" width="8.81640625" style="20"/>
+    <col min="16" max="16384" width="8.81640625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -12798,7 +12750,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46252.6875</v>
       </c>
@@ -12838,7 +12790,7 @@
       </c>
       <c r="O2" s="19"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>46252.6875</v>
       </c>
@@ -12878,7 +12830,7 @@
       </c>
       <c r="O3" s="19"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -12916,7 +12868,7 @@
       </c>
       <c r="O4" s="19"/>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>46260.375509259262</v>
       </c>
@@ -12963,7 +12915,7 @@
       </c>
       <c r="O5" s="20"/>
     </row>
-    <row r="6" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>46260.375509259262</v>
       </c>
@@ -13010,7 +12962,7 @@
       </c>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -13050,7 +13002,7 @@
       </c>
       <c r="O7" s="19"/>
     </row>
-    <row r="8" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>46260.375543981485</v>
       </c>
@@ -13097,7 +13049,7 @@
       </c>
       <c r="O8" s="20"/>
     </row>
-    <row r="9" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>150</v>
       </c>
@@ -13139,7 +13091,7 @@
       </c>
       <c r="O9" s="19"/>
     </row>
-    <row r="10" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -13179,7 +13131,7 @@
       </c>
       <c r="O10" s="19"/>
     </row>
-    <row r="11" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -13219,7 +13171,7 @@
       </c>
       <c r="O11" s="19"/>
     </row>
-    <row r="12" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -13257,7 +13209,7 @@
       </c>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="3">
         <v>46252.6875</v>
       </c>
@@ -13295,7 +13247,7 @@
       </c>
       <c r="O13" s="19"/>
     </row>
-    <row r="14" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -13335,7 +13287,7 @@
       </c>
       <c r="O14" s="19"/>
     </row>
-    <row r="15" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="3">
         <v>46252.6875</v>
       </c>
@@ -13373,7 +13325,7 @@
       </c>
       <c r="O15" s="19"/>
     </row>
-    <row r="16" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
@@ -13413,7 +13365,7 @@
       </c>
       <c r="O16" s="19"/>
     </row>
-    <row r="17" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -13453,7 +13405,7 @@
       </c>
       <c r="O17" s="19"/>
     </row>
-    <row r="18" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>46258.613194444442</v>
       </c>
@@ -13500,7 +13452,7 @@
       </c>
       <c r="O18" s="20"/>
     </row>
-    <row r="19" spans="1:15" s="57" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" s="57" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="49">
         <v>46255</v>
       </c>
@@ -13547,7 +13499,7 @@
       </c>
       <c r="O19" s="55"/>
     </row>
-    <row r="20" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -13587,7 +13539,7 @@
       </c>
       <c r="O20" s="19"/>
     </row>
-    <row r="21" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="6" t="s">
         <v>62</v>
       </c>
@@ -13627,7 +13579,7 @@
       </c>
       <c r="O21" s="19"/>
     </row>
-    <row r="22" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
@@ -13665,7 +13617,7 @@
       </c>
       <c r="O22" s="19"/>
     </row>
-    <row r="23" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
@@ -13703,7 +13655,7 @@
       </c>
       <c r="O23" s="19"/>
     </row>
-    <row r="24" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>46252.6875</v>
       </c>
@@ -13741,7 +13693,7 @@
       </c>
       <c r="O24" s="19"/>
     </row>
-    <row r="25" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>62</v>
       </c>
@@ -13781,7 +13733,7 @@
       </c>
       <c r="O25" s="19"/>
     </row>
-    <row r="26" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -13828,7 +13780,7 @@
       </c>
       <c r="O26" s="20"/>
     </row>
-    <row r="27" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -13875,7 +13827,7 @@
       </c>
       <c r="O27" s="20"/>
     </row>
-    <row r="28" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>62</v>
       </c>
@@ -13913,7 +13865,7 @@
       </c>
       <c r="O28" s="19"/>
     </row>
-    <row r="29" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
@@ -13951,7 +13903,7 @@
       </c>
       <c r="O29" s="19"/>
     </row>
-    <row r="30" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -13993,7 +13945,7 @@
       </c>
       <c r="O30" s="19"/>
     </row>
-    <row r="31" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="22">
         <v>46255</v>
       </c>
@@ -14040,7 +13992,7 @@
       </c>
       <c r="O31" s="20"/>
     </row>
-    <row r="32" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>46258.459722222222</v>
       </c>
@@ -14087,7 +14039,7 @@
       </c>
       <c r="O32" s="20"/>
     </row>
-    <row r="33" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="6" t="s">
         <v>62</v>
       </c>
@@ -14125,7 +14077,7 @@
       </c>
       <c r="O33" s="19"/>
     </row>
-    <row r="34" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <v>46254.375</v>
       </c>
@@ -14167,7 +14119,7 @@
       </c>
       <c r="O34" s="19"/>
     </row>
-    <row r="35" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -14207,7 +14159,7 @@
       </c>
       <c r="O35" s="19"/>
     </row>
-    <row r="36" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -14254,7 +14206,7 @@
       </c>
       <c r="O36" s="20"/>
     </row>
-    <row r="37" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -14292,7 +14244,7 @@
       </c>
       <c r="O37" s="19"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>46252.6875</v>
       </c>
@@ -14332,7 +14284,7 @@
       </c>
       <c r="O38" s="19"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <v>46252.6875</v>
       </c>
@@ -14372,7 +14324,7 @@
       </c>
       <c r="O39" s="19"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="6" t="s">
         <v>62</v>
       </c>
@@ -14410,7 +14362,7 @@
       </c>
       <c r="O40" s="19"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -14450,7 +14402,7 @@
       </c>
       <c r="O41" s="19"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -14490,7 +14442,7 @@
       </c>
       <c r="O42" s="19"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="6" t="s">
         <v>62</v>
       </c>
@@ -14528,7 +14480,7 @@
       </c>
       <c r="O43" s="19"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
         <v>62</v>
       </c>
@@ -14566,7 +14518,7 @@
       </c>
       <c r="O44" s="19"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="6" t="s">
         <v>62</v>
       </c>
@@ -14604,7 +14556,7 @@
       </c>
       <c r="O45" s="19"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -14651,7 +14603,7 @@
       </c>
       <c r="O46" s="20"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <v>46260.375543981485</v>
       </c>
@@ -14698,7 +14650,7 @@
       </c>
       <c r="O47" s="20"/>
     </row>
-    <row r="48" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="6" t="s">
         <v>62</v>
       </c>
@@ -14736,7 +14688,7 @@
       </c>
       <c r="O48" s="19"/>
     </row>
-    <row r="49" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="6" t="s">
         <v>62</v>
       </c>
@@ -14774,7 +14726,7 @@
       </c>
       <c r="O49" s="19"/>
     </row>
-    <row r="50" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="6" t="s">
         <v>62</v>
       </c>
@@ -14812,7 +14764,7 @@
       </c>
       <c r="O50" s="19"/>
     </row>
-    <row r="51" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -14850,7 +14802,7 @@
       </c>
       <c r="O51" s="19"/>
     </row>
-    <row r="52" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="6" t="s">
         <v>62</v>
       </c>
@@ -14888,7 +14840,7 @@
       </c>
       <c r="O52" s="19"/>
     </row>
-    <row r="53" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="3">
         <v>46260.375567129631</v>
       </c>
@@ -14935,7 +14887,7 @@
       </c>
       <c r="O53" s="20"/>
     </row>
-    <row r="54" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
@@ -14973,7 +14925,7 @@
       </c>
       <c r="O54" s="19"/>
     </row>
-    <row r="55" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="3">
         <v>46253.375</v>
       </c>
@@ -15013,7 +14965,7 @@
       </c>
       <c r="O55" s="19"/>
     </row>
-    <row r="56" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
@@ -15051,7 +15003,7 @@
       </c>
       <c r="O56" s="19"/>
     </row>
-    <row r="57" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -15091,7 +15043,7 @@
       </c>
       <c r="O57" s="19"/>
     </row>
-    <row r="58" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="6" t="s">
         <v>62</v>
       </c>
@@ -15129,7 +15081,7 @@
       </c>
       <c r="O58" s="19"/>
     </row>
-    <row r="59" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6" t="s">
         <v>62</v>
       </c>
@@ -15167,7 +15119,7 @@
       </c>
       <c r="O59" s="19"/>
     </row>
-    <row r="60" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
@@ -15205,7 +15157,7 @@
       </c>
       <c r="O60" s="19"/>
     </row>
-    <row r="61" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="3">
         <v>46252.6875</v>
       </c>
@@ -15243,7 +15195,7 @@
       </c>
       <c r="O61" s="19"/>
     </row>
-    <row r="62" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="3">
         <v>46254.385416666664</v>
       </c>
@@ -15285,7 +15237,7 @@
       </c>
       <c r="O62" s="19"/>
     </row>
-    <row r="63" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
@@ -15323,7 +15275,7 @@
       </c>
       <c r="O63" s="19"/>
     </row>
-    <row r="64" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
@@ -15361,7 +15313,7 @@
       </c>
       <c r="O64" s="19"/>
     </row>
-    <row r="65" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="6" t="s">
         <v>62</v>
       </c>
@@ -15399,7 +15351,7 @@
       </c>
       <c r="O65" s="19"/>
     </row>
-    <row r="66" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -15439,7 +15391,7 @@
       </c>
       <c r="O66" s="19"/>
     </row>
-    <row r="67" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -15479,7 +15431,7 @@
       </c>
       <c r="O67" s="19"/>
     </row>
-    <row r="68" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="6" t="s">
         <v>62</v>
       </c>
@@ -15517,7 +15469,7 @@
       </c>
       <c r="O68" s="19"/>
     </row>
-    <row r="69" spans="1:15" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
@@ -15555,7 +15507,7 @@
       </c>
       <c r="O69" s="19"/>
     </row>
-    <row r="70" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="6" t="s">
         <v>62</v>
       </c>
@@ -15593,7 +15545,7 @@
       </c>
       <c r="O70" s="19"/>
     </row>
-    <row r="71" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -15640,7 +15592,7 @@
       </c>
       <c r="O71" s="20"/>
     </row>
-    <row r="72" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
@@ -15678,7 +15630,7 @@
       </c>
       <c r="O72" s="19"/>
     </row>
-    <row r="73" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -15718,7 +15670,7 @@
       </c>
       <c r="O73" s="19"/>
     </row>
-    <row r="74" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -15765,45 +15717,45 @@
       </c>
       <c r="O74" s="20"/>
     </row>
-    <row r="75" spans="1:15" s="58" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="61" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="62" t="s">
+    <row r="75" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C75" s="62" t="s">
-        <v>10</v>
-      </c>
-      <c r="D75" s="63">
+      <c r="C75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75" s="4">
         <v>150</v>
       </c>
-      <c r="E75" s="63">
+      <c r="E75" s="4">
         <v>214</v>
       </c>
-      <c r="F75" s="63">
+      <c r="F75" s="4">
         <v>-7.0857936779999999</v>
       </c>
-      <c r="G75" s="64" t="s">
+      <c r="G75" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H75" s="65">
+      <c r="H75" s="5">
         <v>230.32</v>
       </c>
-      <c r="I75" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="J75" s="66"/>
-      <c r="K75" s="67"/>
-      <c r="L75" s="67"/>
-      <c r="M75" s="67"/>
-      <c r="N75" s="58" t="str">
+      <c r="I75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J75" s="25"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+      <c r="M75" s="19"/>
+      <c r="N75" t="str">
         <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
-      <c r="O75" s="67"/>
-    </row>
-    <row r="76" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O75" s="19"/>
+    </row>
+    <row r="76" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="6" t="s">
         <v>62</v>
       </c>
@@ -15841,7 +15793,7 @@
       </c>
       <c r="O76" s="19"/>
     </row>
-    <row r="77" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="6" t="s">
         <v>62</v>
       </c>
@@ -15879,7 +15831,7 @@
       </c>
       <c r="O77" s="19"/>
     </row>
-    <row r="78" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -15919,7 +15871,7 @@
       </c>
       <c r="O78" s="19"/>
     </row>
-    <row r="79" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -15957,7 +15909,7 @@
       </c>
       <c r="O79" s="19"/>
     </row>
-    <row r="80" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
@@ -15995,7 +15947,7 @@
       </c>
       <c r="O80" s="19"/>
     </row>
-    <row r="81" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="6" t="s">
         <v>62</v>
       </c>
@@ -16033,7 +15985,7 @@
       </c>
       <c r="O81" s="19"/>
     </row>
-    <row r="82" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="6" t="s">
         <v>62</v>
       </c>
@@ -16071,7 +16023,7 @@
       </c>
       <c r="O82" s="19"/>
     </row>
-    <row r="83" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -16109,7 +16061,7 @@
       </c>
       <c r="O83" s="19"/>
     </row>
-    <row r="84" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="6" t="s">
         <v>62</v>
       </c>
@@ -16147,7 +16099,7 @@
       </c>
       <c r="O84" s="19"/>
     </row>
-    <row r="85" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -16185,7 +16137,7 @@
       </c>
       <c r="O85" s="19"/>
     </row>
-    <row r="86" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
         <v>46252.6875</v>
       </c>
@@ -16225,7 +16177,7 @@
       </c>
       <c r="O86" s="19"/>
     </row>
-    <row r="87" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
@@ -16263,7 +16215,7 @@
       </c>
       <c r="O87" s="19"/>
     </row>
-    <row r="88" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
@@ -16301,7 +16253,7 @@
       </c>
       <c r="O88" s="19"/>
     </row>
-    <row r="89" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -16341,7 +16293,7 @@
       </c>
       <c r="O89" s="19"/>
     </row>
-    <row r="90" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -16379,7 +16331,7 @@
       </c>
       <c r="O90" s="19"/>
     </row>
-    <row r="91" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="22">
         <v>46255</v>
       </c>
@@ -16426,7 +16378,7 @@
       </c>
       <c r="O91" s="20"/>
     </row>
-    <row r="92" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="6" t="s">
         <v>62</v>
       </c>
@@ -16464,7 +16416,7 @@
       </c>
       <c r="O92" s="19"/>
     </row>
-    <row r="93" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="6" t="s">
         <v>62</v>
       </c>
@@ -16502,7 +16454,7 @@
       </c>
       <c r="O93" s="19"/>
     </row>
-    <row r="94" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="6" t="s">
         <v>62</v>
       </c>
@@ -16540,7 +16492,7 @@
       </c>
       <c r="O94" s="19"/>
     </row>
-    <row r="95" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="3">
         <v>46252.6875</v>
       </c>
@@ -16578,7 +16530,7 @@
       </c>
       <c r="O95" s="19"/>
     </row>
-    <row r="96" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="6" t="s">
         <v>62</v>
       </c>
@@ -16616,7 +16568,7 @@
       </c>
       <c r="O96" s="19"/>
     </row>
-    <row r="97" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="3">
         <v>46253.416666666664</v>
       </c>
@@ -16656,7 +16608,7 @@
       </c>
       <c r="O97" s="19"/>
     </row>
-    <row r="98" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -16694,7 +16646,7 @@
       </c>
       <c r="O98" s="19"/>
     </row>
-    <row r="99" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46254.375</v>
       </c>
@@ -16736,7 +16688,7 @@
       </c>
       <c r="O99" s="19"/>
     </row>
-    <row r="100" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="6" t="s">
         <v>62</v>
       </c>
@@ -16774,7 +16726,7 @@
       </c>
       <c r="O100" s="19"/>
     </row>
-    <row r="101" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6" t="s">
         <v>62</v>
       </c>
@@ -16812,7 +16764,7 @@
       </c>
       <c r="O101" s="19"/>
     </row>
-    <row r="102" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A102" s="6" t="s">
         <v>62</v>
       </c>
@@ -16852,7 +16804,7 @@
       </c>
       <c r="O102" s="19"/>
     </row>
-    <row r="103" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="6" t="s">
         <v>62</v>
       </c>
@@ -16890,7 +16842,7 @@
       </c>
       <c r="O103" s="19"/>
     </row>
-    <row r="104" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A104" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -16928,7 +16880,7 @@
       </c>
       <c r="O104" s="19"/>
     </row>
-    <row r="105" spans="1:15" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A105" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -16966,7 +16918,7 @@
       </c>
       <c r="O105" s="19"/>
     </row>
-    <row r="106" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="3">
         <v>46252.6875</v>
       </c>
@@ -17004,7 +16956,7 @@
       </c>
       <c r="O106" s="19"/>
     </row>
-    <row r="107" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="6" t="s">
         <v>62</v>
       </c>
@@ -17042,7 +16994,7 @@
       </c>
       <c r="O107" s="19"/>
     </row>
-    <row r="108" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="6" t="s">
         <v>62</v>
       </c>
@@ -17082,7 +17034,7 @@
       </c>
       <c r="O108" s="19"/>
     </row>
-    <row r="109" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="6" t="s">
         <v>62</v>
       </c>
@@ -17120,7 +17072,7 @@
       </c>
       <c r="O109" s="19"/>
     </row>
-    <row r="110" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="6" t="s">
         <v>62</v>
       </c>
@@ -17158,7 +17110,7 @@
       </c>
       <c r="O110" s="19"/>
     </row>
-    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A111" s="6" t="s">
         <v>62</v>
       </c>
@@ -17196,7 +17148,7 @@
       </c>
       <c r="O111" s="19"/>
     </row>
-    <row r="112" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A112" s="6" t="s">
         <v>62</v>
       </c>
@@ -17234,7 +17186,7 @@
       </c>
       <c r="O112" s="19"/>
     </row>
-    <row r="113" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A113" s="6" t="s">
         <v>62</v>
       </c>
@@ -17272,7 +17224,7 @@
       </c>
       <c r="O113" s="19"/>
     </row>
-    <row r="114" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A114" s="6" t="s">
         <v>62</v>
       </c>
@@ -17310,7 +17262,7 @@
       </c>
       <c r="O114" s="19"/>
     </row>
-    <row r="115" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A115" s="6" t="s">
         <v>62</v>
       </c>
@@ -17348,7 +17300,7 @@
       </c>
       <c r="O115" s="19"/>
     </row>
-    <row r="116" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A116" s="3">
         <v>46252.6875</v>
       </c>
@@ -17388,7 +17340,7 @@
       </c>
       <c r="O116" s="19"/>
     </row>
-    <row r="117" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="3">
         <v>46252.6875</v>
       </c>
@@ -17426,7 +17378,7 @@
       </c>
       <c r="O117" s="19"/>
     </row>
-    <row r="118" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A118" s="6" t="s">
         <v>62</v>
       </c>
@@ -17464,7 +17416,7 @@
       </c>
       <c r="O118" s="19"/>
     </row>
-    <row r="119" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A119" s="6" t="s">
         <v>62</v>
       </c>
@@ -17502,7 +17454,7 @@
       </c>
       <c r="O119" s="19"/>
     </row>
-    <row r="120" spans="1:15" s="31" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:15" s="31" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A120" s="6" t="s">
         <v>62</v>
       </c>
@@ -17540,7 +17492,7 @@
       </c>
       <c r="O120" s="19"/>
     </row>
-    <row r="121" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A121" s="6" t="s">
         <v>62</v>
       </c>
@@ -17578,7 +17530,7 @@
       </c>
       <c r="O121" s="19"/>
     </row>
-    <row r="122" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="6" t="s">
         <v>62</v>
       </c>
@@ -17616,7 +17568,7 @@
       </c>
       <c r="O122" s="19"/>
     </row>
-    <row r="123" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A123" s="6" t="s">
         <v>62</v>
       </c>
@@ -17656,7 +17608,7 @@
       </c>
       <c r="O123" s="19"/>
     </row>
-    <row r="124" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="6" t="s">
         <v>62</v>
       </c>
@@ -17696,7 +17648,7 @@
       </c>
       <c r="O124" s="19"/>
     </row>
-    <row r="125" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A125" s="6" t="s">
         <v>62</v>
       </c>
@@ -17734,7 +17686,7 @@
       </c>
       <c r="O125" s="19"/>
     </row>
-    <row r="126" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A126" s="6" t="s">
         <v>62</v>
       </c>
@@ -17772,7 +17724,7 @@
       </c>
       <c r="O126" s="19"/>
     </row>
-    <row r="127" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="6" t="s">
         <v>62</v>
       </c>
@@ -17812,7 +17764,7 @@
       </c>
       <c r="O127" s="19"/>
     </row>
-    <row r="128" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A128" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -17850,7 +17802,7 @@
       </c>
       <c r="O128" s="19"/>
     </row>
-    <row r="129" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A129" s="6" t="s">
         <v>62</v>
       </c>
@@ -17888,7 +17840,7 @@
       </c>
       <c r="O129" s="19"/>
     </row>
-    <row r="130" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A130" s="6" t="s">
         <v>62</v>
       </c>
@@ -17926,7 +17878,7 @@
       </c>
       <c r="O130" s="19"/>
     </row>
-    <row r="131" spans="1:15" s="21" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:15" s="21" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A131" s="6" t="s">
         <v>62</v>
       </c>
@@ -17964,7 +17916,7 @@
       </c>
       <c r="O131" s="19"/>
     </row>
-    <row r="132" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A132" s="6" t="s">
         <v>62</v>
       </c>
@@ -18002,7 +17954,7 @@
       </c>
       <c r="O132" s="19"/>
     </row>
-    <row r="133" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A133" s="6" t="s">
         <v>62</v>
       </c>
@@ -18041,7 +17993,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="6" t="s">
         <v>62</v>
       </c>
@@ -18079,7 +18031,7 @@
       </c>
       <c r="O134" s="19"/>
     </row>
-    <row r="135" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -18117,7 +18069,7 @@
       </c>
       <c r="O135" s="19"/>
     </row>
-    <row r="136" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A136" s="6" t="s">
         <v>62</v>
       </c>
@@ -18155,7 +18107,7 @@
       </c>
       <c r="O136" s="19"/>
     </row>
-    <row r="137" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="6" t="s">
         <v>62</v>
       </c>
@@ -18192,7 +18144,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="6" t="s">
         <v>62</v>
       </c>
@@ -18229,7 +18181,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="139" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A139" s="6" t="s">
         <v>62</v>
       </c>
@@ -18267,7 +18219,7 @@
       </c>
       <c r="O139" s="19"/>
     </row>
-    <row r="140" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A140" s="6" t="s">
         <v>62</v>
       </c>
@@ -18304,7 +18256,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="141" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A141" s="6" t="s">
         <v>62</v>
       </c>
@@ -18343,7 +18295,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="10" t="s">
         <v>62</v>
       </c>
@@ -18379,7 +18331,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="143" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A143" s="13">
         <v>46253.375</v>
       </c>
@@ -18418,7 +18370,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="144" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -18459,7 +18411,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -18505,7 +18457,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="146" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A146" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -18539,7 +18491,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="147" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A147" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -18575,7 +18527,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="148" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="3">
         <v>46260.375659722224</v>
       </c>
@@ -18621,7 +18573,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="149" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A149" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -18657,7 +18609,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="150" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A150" s="13">
         <v>46252.6875</v>
       </c>
@@ -18693,7 +18645,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="151" spans="1:15" s="31" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:15" s="31" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A151" s="33">
         <v>46260.634351851855</v>
       </c>
@@ -18742,7 +18694,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="152" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A152" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -18776,7 +18728,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="153" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A153" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -18811,7 +18763,7 @@
       </c>
       <c r="O153" s="12"/>
     </row>
-    <row r="154" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="13">
         <v>46252.645833333336</v>
       </c>
@@ -18845,7 +18797,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="47" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:15" s="47" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A155" s="39">
         <v>46260.425902777781</v>
       </c>
@@ -18892,7 +18844,7 @@
       </c>
       <c r="O155" s="45"/>
     </row>
-    <row r="156" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -18928,7 +18880,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A157" s="13">
         <v>46252.645833333336</v>
       </c>
@@ -18962,7 +18914,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="158" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A158" s="13">
         <v>46252.6875</v>
       </c>
@@ -18996,7 +18948,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="159" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A159" s="3">
         <v>46260.557557870372</v>
       </c>
@@ -19042,7 +18994,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="160" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A160" s="3">
         <v>46258.443055555559</v>
       </c>
@@ -19088,7 +19040,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
         <v>46259.375</v>
       </c>
@@ -19134,7 +19086,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="10" t="s">
         <v>62</v>
       </c>
@@ -19171,7 +19123,7 @@
       </c>
       <c r="O162" s="12"/>
     </row>
-    <row r="163" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -19207,7 +19159,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A164" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -19242,7 +19194,7 @@
       </c>
       <c r="O164" s="12"/>
     </row>
-    <row r="165" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A165" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -19276,7 +19228,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="166" spans="1:15" s="31" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:15" s="31" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A166" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -19323,7 +19275,7 @@
       </c>
       <c r="O166" s="20"/>
     </row>
-    <row r="167" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A167" s="22">
         <v>46255</v>
       </c>
@@ -19369,7 +19321,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="168" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A168" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -19406,7 +19358,7 @@
       </c>
       <c r="O168" s="12"/>
     </row>
-    <row r="169" spans="1:15" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A169" s="13">
         <v>46252.6875</v>
       </c>
@@ -19442,7 +19394,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A170" s="10" t="s">
         <v>62</v>
       </c>
@@ -19476,7 +19428,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="171" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A171" s="3">
         <v>46260.555173611108</v>
       </c>
@@ -19522,7 +19474,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="172" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A172" s="13">
         <v>46252.645138888889</v>
       </c>
@@ -19558,7 +19510,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="173" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="3">
         <v>46258.443749999999</v>
       </c>
@@ -19604,7 +19556,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="174" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A174" s="13">
         <v>46253.4</v>
       </c>
@@ -19643,7 +19595,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="175" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A175" s="10" t="s">
         <v>62</v>
       </c>
@@ -19680,7 +19632,7 @@
       </c>
       <c r="O175" s="12"/>
     </row>
-    <row r="176" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -19717,7 +19669,7 @@
       </c>
       <c r="O176" s="12"/>
     </row>
-    <row r="177" spans="1:15" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A177" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -19752,7 +19704,7 @@
       </c>
       <c r="O177" s="12"/>
     </row>
-    <row r="178" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A178" s="10" t="s">
         <v>62</v>
       </c>
@@ -19789,7 +19741,7 @@
       </c>
       <c r="O178" s="12"/>
     </row>
-    <row r="179" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A179" s="10" t="s">
         <v>62</v>
       </c>
@@ -19825,7 +19777,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="180" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A180" s="3">
         <v>46260.375671296293</v>
       </c>
@@ -19871,7 +19823,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="181" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A181" s="3">
         <v>46259.375</v>
       </c>
@@ -19917,7 +19869,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:15" ht="15.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A182" s="3">
         <v>46260.558067129627</v>
       </c>
@@ -19963,7 +19915,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A183" s="13">
         <v>46252.6875</v>
       </c>
@@ -20000,7 +19952,7 @@
       </c>
       <c r="O183" s="12"/>
     </row>
-    <row r="184" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A184" s="13">
         <v>46252.6875</v>
       </c>
@@ -20036,7 +19988,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="185" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A185" s="10" t="s">
         <v>62</v>
       </c>
@@ -20071,7 +20023,7 @@
       </c>
       <c r="O185" s="12"/>
     </row>
-    <row r="186" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -20106,7 +20058,7 @@
       </c>
       <c r="O186" s="12"/>
     </row>
-    <row r="187" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A187" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -20142,7 +20094,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="188" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A188" s="3">
         <v>46260.55133101852</v>
       </c>
@@ -20188,7 +20140,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="189" spans="1:15" s="31" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" s="31" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A189" s="33">
         <v>46259.375</v>
       </c>
@@ -20237,7 +20189,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="190" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A190" s="10" t="s">
         <v>62</v>
       </c>
@@ -20272,7 +20224,7 @@
       </c>
       <c r="O190" s="12"/>
     </row>
-    <row r="191" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="10" t="s">
         <v>62</v>
       </c>
@@ -20307,7 +20259,7 @@
       </c>
       <c r="O191" s="12"/>
     </row>
-    <row r="192" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:15" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A192" s="3">
         <v>46260.375636574077</v>
       </c>
@@ -20353,7 +20305,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="193" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="13">
         <v>46252.6875</v>
       </c>
@@ -20393,7 +20345,7 @@
       </c>
       <c r="O193" s="12"/>
     </row>
-    <row r="194" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="10" t="s">
         <v>62</v>
       </c>
@@ -20433,7 +20385,7 @@
       </c>
       <c r="O194" s="12"/>
     </row>
-    <row r="195" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A195" s="10" t="s">
         <v>62</v>
       </c>
@@ -20473,7 +20425,7 @@
       </c>
       <c r="O195" s="12"/>
     </row>
-    <row r="196" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A196" s="10" t="s">
         <v>62</v>
       </c>
@@ -20513,7 +20465,7 @@
       </c>
       <c r="O196" s="12"/>
     </row>
-    <row r="197" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A197" s="10" t="s">
         <v>62</v>
       </c>
@@ -20551,7 +20503,7 @@
       </c>
       <c r="O197" s="12"/>
     </row>
-    <row r="198" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A198" s="10" t="s">
         <v>62</v>
       </c>
@@ -20591,7 +20543,7 @@
       </c>
       <c r="O198" s="12"/>
     </row>
-    <row r="199" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A199" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -20638,7 +20590,7 @@
       </c>
       <c r="O199" s="20"/>
     </row>
-    <row r="200" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A200" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -20680,7 +20632,7 @@
       </c>
       <c r="O200" s="20"/>
     </row>
-    <row r="201" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="13">
         <v>46252.6875</v>
       </c>
@@ -20717,7 +20669,7 @@
       </c>
       <c r="O201" s="12"/>
     </row>
-    <row r="202" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A202" s="10" t="s">
         <v>62</v>
       </c>
@@ -20752,7 +20704,7 @@
       </c>
       <c r="O202" s="12"/>
     </row>
-    <row r="203" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A203" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -20787,7 +20739,7 @@
       </c>
       <c r="O203" s="12"/>
     </row>
-    <row r="204" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A204" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -20824,7 +20776,7 @@
       </c>
       <c r="O204" s="12"/>
     </row>
-    <row r="205" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A205" s="10" t="s">
         <v>62</v>
       </c>
@@ -20858,7 +20810,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="206" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A206" s="22">
         <v>46255</v>
       </c>
@@ -20904,7 +20856,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="207" spans="1:15" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" s="21" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A207" s="10" t="s">
         <v>62</v>
       </c>
@@ -20944,7 +20896,7 @@
       </c>
       <c r="O207" s="12"/>
     </row>
-    <row r="208" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="13">
         <v>46252.635416666664</v>
       </c>
@@ -20981,7 +20933,7 @@
       </c>
       <c r="O208" s="12"/>
     </row>
-    <row r="209" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="10" t="s">
         <v>62</v>
       </c>
@@ -21016,7 +20968,7 @@
       </c>
       <c r="O209" s="12"/>
     </row>
-    <row r="210" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A210" s="10" t="s">
         <v>62</v>
       </c>
@@ -21051,7 +21003,7 @@
       </c>
       <c r="O210" s="12"/>
     </row>
-    <row r="211" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A211" s="10" t="s">
         <v>62</v>
       </c>
@@ -21086,7 +21038,7 @@
       </c>
       <c r="O211" s="12"/>
     </row>
-    <row r="212" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="10" t="s">
         <v>62</v>
       </c>
@@ -21121,7 +21073,7 @@
       </c>
       <c r="O212" s="12"/>
     </row>
-    <row r="213" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A213" s="13">
         <v>46252.688194444447</v>
       </c>
@@ -21157,7 +21109,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A214" s="10" t="s">
         <v>62</v>
       </c>
@@ -21192,7 +21144,7 @@
       </c>
       <c r="O214" s="12"/>
     </row>
-    <row r="215" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A215" s="10" t="s">
         <v>62</v>
       </c>
@@ -21227,7 +21179,7 @@
       </c>
       <c r="O215" s="12"/>
     </row>
-    <row r="216" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A216" s="10" t="s">
         <v>62</v>
       </c>
@@ -21261,7 +21213,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="217" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A217" s="10" t="s">
         <v>62</v>
       </c>
@@ -21298,7 +21250,7 @@
       </c>
       <c r="O217" s="12"/>
     </row>
-    <row r="218" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="13">
         <v>46253.375</v>
       </c>
@@ -21336,7 +21288,7 @@
       </c>
       <c r="O218" s="12"/>
     </row>
-    <row r="219" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A219" s="10" t="s">
         <v>62</v>
       </c>
@@ -21373,7 +21325,7 @@
       </c>
       <c r="O219" s="12"/>
     </row>
-    <row r="220" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A220" s="10" t="s">
         <v>62</v>
       </c>
@@ -21408,7 +21360,7 @@
       </c>
       <c r="O220" s="12"/>
     </row>
-    <row r="221" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A221" s="10" t="s">
         <v>62</v>
       </c>
@@ -21443,7 +21395,7 @@
       </c>
       <c r="O221" s="12"/>
     </row>
-    <row r="222" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A222" s="10" t="s">
         <v>62</v>
       </c>
@@ -21480,7 +21432,7 @@
       </c>
       <c r="O222" s="12"/>
     </row>
-    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="22">
         <v>46255</v>
       </c>
@@ -21526,7 +21478,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A224" s="10" t="s">
         <v>62</v>
       </c>
@@ -21561,7 +21513,7 @@
       </c>
       <c r="O224" s="12"/>
     </row>
-    <row r="225" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A225" s="10" t="s">
         <v>62</v>
       </c>
@@ -21598,7 +21550,7 @@
       </c>
       <c r="O225" s="12"/>
     </row>
-    <row r="226" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="10" t="s">
         <v>62</v>
       </c>
@@ -21633,7 +21585,7 @@
       </c>
       <c r="O226" s="12"/>
     </row>
-    <row r="227" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="13">
         <v>46252.6875</v>
       </c>
@@ -21669,7 +21621,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="228" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A228" s="10" t="s">
         <v>62</v>
       </c>
@@ -21704,7 +21656,7 @@
       </c>
       <c r="O228" s="12"/>
     </row>
-    <row r="229" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A229" s="10" t="s">
         <v>62</v>
       </c>
@@ -21739,7 +21691,7 @@
       </c>
       <c r="O229" s="12"/>
     </row>
-    <row r="230" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A230" s="10" t="s">
         <v>62</v>
       </c>
@@ -21776,7 +21728,7 @@
       </c>
       <c r="O230" s="12"/>
     </row>
-    <row r="231" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A231" s="10" t="s">
         <v>62</v>
       </c>
@@ -21811,7 +21763,7 @@
       </c>
       <c r="O231" s="12"/>
     </row>
-    <row r="232" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="10" t="s">
         <v>62</v>
       </c>
@@ -21845,7 +21797,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="233" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -21891,7 +21843,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="234" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A234" s="10" t="s">
         <v>62</v>
       </c>
@@ -21925,7 +21877,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="235" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="10" t="s">
         <v>62</v>
       </c>
@@ -21960,7 +21912,7 @@
       </c>
       <c r="O235" s="12"/>
     </row>
-    <row r="236" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A236" s="10" t="s">
         <v>62</v>
       </c>
@@ -21995,7 +21947,7 @@
       </c>
       <c r="O236" s="12"/>
     </row>
-    <row r="237" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="10" t="s">
         <v>62</v>
       </c>
@@ -22030,7 +21982,7 @@
       </c>
       <c r="O237" s="19"/>
     </row>
-    <row r="238" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A238" s="10" t="s">
         <v>62</v>
       </c>
@@ -22065,7 +22017,7 @@
       </c>
       <c r="O238" s="12"/>
     </row>
-    <row r="239" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A239" s="10" t="s">
         <v>62</v>
       </c>
@@ -22102,7 +22054,7 @@
       </c>
       <c r="O239" s="19"/>
     </row>
-    <row r="240" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A240" s="10" t="s">
         <v>62</v>
       </c>
@@ -22137,7 +22089,7 @@
       </c>
       <c r="O240" s="12"/>
     </row>
-    <row r="241" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A241" s="10" t="s">
         <v>62</v>
       </c>
@@ -22173,7 +22125,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="242" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A242" s="10" t="s">
         <v>62</v>
       </c>
@@ -22207,7 +22159,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A243" s="11" t="s">
         <v>62</v>
       </c>
@@ -22242,7 +22194,7 @@
       </c>
       <c r="O243" s="19"/>
     </row>
-    <row r="244" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A244" s="10" t="s">
         <v>62</v>
       </c>
@@ -22277,7 +22229,7 @@
       </c>
       <c r="O244" s="12"/>
     </row>
-    <row r="245" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A245" s="10" t="s">
         <v>62</v>
       </c>
@@ -22312,7 +22264,7 @@
       </c>
       <c r="O245" s="19"/>
     </row>
-    <row r="246" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A246" s="10" t="s">
         <v>62</v>
       </c>
@@ -22347,7 +22299,7 @@
       </c>
       <c r="O246" s="12"/>
     </row>
-    <row r="247" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A247" s="10" t="s">
         <v>62</v>
       </c>
@@ -22384,7 +22336,7 @@
       </c>
       <c r="O247" s="19"/>
     </row>
-    <row r="248" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A248" s="10" t="s">
         <v>62</v>
       </c>
@@ -22419,7 +22371,7 @@
       </c>
       <c r="O248" s="19"/>
     </row>
-    <row r="249" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A249" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -22465,7 +22417,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A250" s="10" t="s">
         <v>62</v>
       </c>
@@ -22500,7 +22452,7 @@
       </c>
       <c r="O250" s="19"/>
     </row>
-    <row r="251" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="13">
         <v>46251.506249999999</v>
       </c>
@@ -22535,7 +22487,7 @@
       </c>
       <c r="O251" s="19"/>
     </row>
-    <row r="252" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A252" s="10" t="s">
         <v>62</v>
       </c>
@@ -22570,7 +22522,7 @@
       </c>
       <c r="O252" s="19"/>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>197</v>
       </c>
@@ -22605,7 +22557,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>198</v>
       </c>
@@ -22640,7 +22592,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>199</v>
       </c>
@@ -22675,7 +22627,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>199</v>
       </c>
@@ -22710,7 +22662,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>200</v>
       </c>
@@ -22745,43 +22697,42 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="258" spans="1:15" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="58" t="s">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
         <v>201</v>
       </c>
-      <c r="B258" s="58" t="s">
+      <c r="B258" t="s">
         <v>19</v>
       </c>
-      <c r="C258" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D258" s="58">
+      <c r="C258" t="s">
+        <v>7</v>
+      </c>
+      <c r="D258">
         <v>20</v>
       </c>
-      <c r="E258" s="58">
+      <c r="E258">
         <v>241</v>
       </c>
-      <c r="F258" s="58"/>
-      <c r="J258" s="60" t="s">
+      <c r="F258"/>
+      <c r="J258" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="K258" s="60" t="s">
+      <c r="K258" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="L258" s="60">
+      <c r="L258" s="20">
         <v>4520</v>
       </c>
-      <c r="M258" s="60">
+      <c r="M258" s="20">
         <f t="shared" si="4"/>
         <v>300</v>
       </c>
-      <c r="N258" s="59" t="str">
+      <c r="N258" s="12" t="str">
         <f t="shared" ref="N258:N271" si="5">IF(COUNTIFS( $B$2:$B$896, B258, $C$2:$C$896, C258, $D$2:$D$896, D258, $E$2:$E$896, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
-      <c r="O258" s="60"/>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>202</v>
       </c>
@@ -22816,7 +22767,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>203</v>
       </c>
@@ -22851,43 +22802,42 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="261" spans="1:15" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="58" t="s">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
         <v>204</v>
       </c>
-      <c r="B261" s="58" t="s">
+      <c r="B261" t="s">
         <v>36</v>
       </c>
-      <c r="C261" s="58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D261" s="58">
+      <c r="C261" t="s">
+        <v>7</v>
+      </c>
+      <c r="D261">
         <v>5</v>
       </c>
-      <c r="E261" s="58">
+      <c r="E261">
         <v>1251</v>
       </c>
-      <c r="F261" s="58"/>
-      <c r="J261" s="60" t="s">
+      <c r="F261"/>
+      <c r="J261" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="K261" s="60" t="s">
+      <c r="K261" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="L261" s="60">
+      <c r="L261" s="20">
         <v>6005</v>
       </c>
-      <c r="M261" s="60">
+      <c r="M261" s="20">
         <f t="shared" si="4"/>
         <v>250</v>
       </c>
-      <c r="N261" s="59" t="str">
+      <c r="N261" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
-      <c r="O261" s="60"/>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>205</v>
       </c>
@@ -22922,7 +22872,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>204</v>
       </c>
@@ -22957,7 +22907,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>204</v>
       </c>
@@ -22992,7 +22942,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>204</v>
       </c>
@@ -23027,7 +22977,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>204</v>
       </c>
@@ -23062,43 +23012,42 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="267" spans="1:15" s="59" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="58" t="s">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
         <v>206</v>
       </c>
-      <c r="B267" s="58" t="s">
+      <c r="B267" t="s">
         <v>23</v>
       </c>
-      <c r="C267" s="58" t="s">
-        <v>10</v>
-      </c>
-      <c r="D267" s="58">
+      <c r="C267" t="s">
+        <v>10</v>
+      </c>
+      <c r="D267">
         <v>40</v>
       </c>
-      <c r="E267" s="58">
+      <c r="E267">
         <v>211</v>
       </c>
-      <c r="F267" s="58"/>
-      <c r="J267" s="60" t="s">
+      <c r="F267"/>
+      <c r="J267" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="K267" s="60" t="s">
+      <c r="K267" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="L267" s="60">
+      <c r="L267" s="20">
         <v>8760</v>
       </c>
-      <c r="M267" s="60">
+      <c r="M267" s="20">
         <f t="shared" si="4"/>
         <v>320</v>
       </c>
-      <c r="N267" s="59" t="str">
+      <c r="N267" s="12" t="str">
         <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
-      <c r="O267" s="60"/>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>207</v>
       </c>
@@ -23133,7 +23082,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>207</v>
       </c>
@@ -23168,7 +23117,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>208</v>
       </c>
@@ -23203,7 +23152,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>207</v>
       </c>
